--- a/artfynd/A 54495-2025 artfynd.xlsx
+++ b/artfynd/A 54495-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130041585</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130041599</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130041525</v>
+        <v>130041502</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>81073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475108</v>
+        <v>475113</v>
       </c>
       <c r="R4" t="n">
-        <v>6832521</v>
+        <v>6832544</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130041478</v>
+        <v>130041525</v>
       </c>
       <c r="B5" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475186</v>
+        <v>475108</v>
       </c>
       <c r="R5" t="n">
-        <v>6832701</v>
+        <v>6832521</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1106,7 @@
         <v>130041582</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1213,7 @@
         <v>130041579</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130041502</v>
+        <v>130041478</v>
       </c>
       <c r="B8" t="n">
-        <v>81072</v>
+        <v>57740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,34 +1328,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475113</v>
+        <v>475186</v>
       </c>
       <c r="R8" t="n">
-        <v>6832544</v>
+        <v>6832701</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1402,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130041429</v>
+        <v>130041603</v>
       </c>
       <c r="B9" t="n">
-        <v>79706</v>
+        <v>78754</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475441</v>
+        <v>475161</v>
       </c>
       <c r="R9" t="n">
-        <v>6832541</v>
+        <v>6832599</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,7 +1544,7 @@
         <v>130041595</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>130041578</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130041518</v>
+        <v>130041527</v>
       </c>
       <c r="B12" t="n">
-        <v>91619</v>
+        <v>79088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475537</v>
+        <v>475061</v>
       </c>
       <c r="R12" t="n">
-        <v>6832616</v>
+        <v>6832499</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,12 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På kulturved (gammal timmerstomme)</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130041603</v>
+        <v>130041518</v>
       </c>
       <c r="B13" t="n">
-        <v>78753</v>
+        <v>91620</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1902,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475161</v>
+        <v>475537</v>
       </c>
       <c r="R13" t="n">
-        <v>6832599</v>
+        <v>6832616</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1942,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På kulturved (gammal timmerstomme)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130041527</v>
+        <v>130041429</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,21 +1985,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475061</v>
+        <v>475441</v>
       </c>
       <c r="R14" t="n">
-        <v>6832499</v>
+        <v>6832541</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,7 +2084,7 @@
         <v>130041592</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>130041593</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>130041522</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>130041483</v>
       </c>
       <c r="B19" t="n">
-        <v>79111</v>
+        <v>79112</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130041476</v>
+        <v>130041597</v>
       </c>
       <c r="B20" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,39 +2632,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475245</v>
+        <v>475391</v>
       </c>
       <c r="R20" t="n">
-        <v>6832734</v>
+        <v>6832581</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2696,7 +2691,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2706,12 +2701,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2738,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130041442</v>
+        <v>130041543</v>
       </c>
       <c r="B21" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2749,21 +2739,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2773,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475303</v>
+        <v>475124</v>
       </c>
       <c r="R21" t="n">
-        <v>6832754</v>
+        <v>6832639</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2808,7 +2798,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2818,7 +2808,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130041597</v>
+        <v>130041442</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2856,21 +2846,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2880,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475391</v>
+        <v>475303</v>
       </c>
       <c r="R22" t="n">
-        <v>6832581</v>
+        <v>6832754</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2925,7 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,38 +2942,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130041465</v>
+        <v>130041476</v>
       </c>
       <c r="B23" t="n">
-        <v>56930</v>
+        <v>57740</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2992,10 +2982,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475430</v>
+        <v>475245</v>
       </c>
       <c r="R23" t="n">
-        <v>6832587</v>
+        <v>6832734</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3027,7 +3017,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3037,7 +3027,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3064,45 +3059,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130041543</v>
+        <v>130041465</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>56930</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475124</v>
+        <v>475430</v>
       </c>
       <c r="R24" t="n">
-        <v>6832639</v>
+        <v>6832587</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3174,7 +3174,7 @@
         <v>130041590</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>130041572</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130041461</v>
+        <v>130041608</v>
       </c>
       <c r="B27" t="n">
-        <v>57740</v>
+        <v>78491</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,39 +3396,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>475283</v>
+        <v>475113</v>
       </c>
       <c r="R27" t="n">
-        <v>6832744</v>
+        <v>6832544</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3460,7 +3455,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3470,7 +3465,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3497,10 +3492,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130041608</v>
+        <v>130041461</v>
       </c>
       <c r="B28" t="n">
-        <v>78490</v>
+        <v>57740</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3508,34 +3503,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>475113</v>
+        <v>475283</v>
       </c>
       <c r="R28" t="n">
-        <v>6832544</v>
+        <v>6832744</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3607,7 +3607,7 @@
         <v>130041448</v>
       </c>
       <c r="B29" t="n">
-        <v>79119</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3711,10 +3711,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130041473</v>
+        <v>130041573</v>
       </c>
       <c r="B30" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3722,39 +3722,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>475044</v>
+        <v>475283</v>
       </c>
       <c r="R30" t="n">
-        <v>6832743</v>
+        <v>6832815</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3786,7 +3781,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3796,12 +3791,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3828,10 +3818,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130041573</v>
+        <v>130041584</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3863,10 +3853,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>475283</v>
+        <v>475036</v>
       </c>
       <c r="R31" t="n">
-        <v>6832815</v>
+        <v>6832748</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3898,7 +3888,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3908,7 +3898,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3935,10 +3925,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130041584</v>
+        <v>130041473</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3946,34 +3936,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>475036</v>
+        <v>475044</v>
       </c>
       <c r="R32" t="n">
-        <v>6832748</v>
+        <v>6832743</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4005,7 +4000,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4015,7 +4010,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4045,7 +4045,7 @@
         <v>130041602</v>
       </c>
       <c r="B33" t="n">
-        <v>78753</v>
+        <v>78754</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>130041591</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>130041544</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4363,10 +4363,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130041430</v>
+        <v>130041524</v>
       </c>
       <c r="B36" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4374,21 +4374,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>475161</v>
+        <v>475144</v>
       </c>
       <c r="R36" t="n">
-        <v>6832599</v>
+        <v>6832586</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4470,10 +4470,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130041524</v>
+        <v>130041430</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>475144</v>
+        <v>475161</v>
       </c>
       <c r="R37" t="n">
-        <v>6832586</v>
+        <v>6832599</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4580,7 +4580,7 @@
         <v>130041594</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>130041600</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>130041562</v>
       </c>
       <c r="B40" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>130041576</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>130041526</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5112,10 +5112,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130041575</v>
+        <v>130041529</v>
       </c>
       <c r="B43" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>475266</v>
+        <v>475095</v>
       </c>
       <c r="R43" t="n">
-        <v>6832803</v>
+        <v>6832582</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5182,7 +5182,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5219,10 +5219,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130041588</v>
+        <v>130041583</v>
       </c>
       <c r="B44" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5254,10 +5254,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475058</v>
+        <v>475057</v>
       </c>
       <c r="R44" t="n">
-        <v>6832696</v>
+        <v>6832751</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5326,10 +5326,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130041571</v>
+        <v>130041575</v>
       </c>
       <c r="B45" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>475307</v>
+        <v>475266</v>
       </c>
       <c r="R45" t="n">
-        <v>6832773</v>
+        <v>6832803</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5433,10 +5433,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130041529</v>
+        <v>130041588</v>
       </c>
       <c r="B46" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475095</v>
+        <v>475058</v>
       </c>
       <c r="R46" t="n">
-        <v>6832582</v>
+        <v>6832696</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5540,10 +5540,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130041475</v>
+        <v>130041571</v>
       </c>
       <c r="B47" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5551,39 +5551,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>475277</v>
+        <v>475307</v>
       </c>
       <c r="R47" t="n">
-        <v>6832740</v>
+        <v>6832773</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5615,7 +5610,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5625,12 +5620,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran), högst 5 år gamla</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5657,10 +5647,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130041583</v>
+        <v>130041475</v>
       </c>
       <c r="B48" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5668,34 +5658,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>475057</v>
+        <v>475277</v>
       </c>
       <c r="R48" t="n">
-        <v>6832751</v>
+        <v>6832740</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5727,7 +5722,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5737,7 +5732,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran), högst 5 år gamla</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5764,10 +5764,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130041449</v>
+        <v>130041570</v>
       </c>
       <c r="B49" t="n">
-        <v>79119</v>
+        <v>79088</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5775,21 +5775,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>475100</v>
+        <v>475287</v>
       </c>
       <c r="R49" t="n">
-        <v>6832696</v>
+        <v>6832747</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5871,32 +5871,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130041447</v>
+        <v>130041482</v>
       </c>
       <c r="B50" t="n">
-        <v>79119</v>
+        <v>79112</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6434</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>475447</v>
+        <v>475500</v>
       </c>
       <c r="R50" t="n">
-        <v>6832649</v>
+        <v>6832632</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5978,10 +5978,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130041570</v>
+        <v>130041565</v>
       </c>
       <c r="B51" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>475287</v>
+        <v>475456</v>
       </c>
       <c r="R51" t="n">
-        <v>6832747</v>
+        <v>6832651</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6085,10 +6085,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130041450</v>
+        <v>130041596</v>
       </c>
       <c r="B52" t="n">
-        <v>79119</v>
+        <v>79088</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6096,21 +6096,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>475269</v>
+        <v>475378</v>
       </c>
       <c r="R52" t="n">
-        <v>6832659</v>
+        <v>6832576</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6192,10 +6192,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130041458</v>
+        <v>130041577</v>
       </c>
       <c r="B53" t="n">
-        <v>79677</v>
+        <v>79088</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6203,21 +6203,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>475113</v>
+        <v>475162</v>
       </c>
       <c r="R53" t="n">
-        <v>6832543</v>
+        <v>6832756</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6299,32 +6299,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130041482</v>
+        <v>130041498</v>
       </c>
       <c r="B54" t="n">
-        <v>79111</v>
+        <v>78846</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>475500</v>
+        <v>475098</v>
       </c>
       <c r="R54" t="n">
-        <v>6832632</v>
+        <v>6832700</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6406,10 +6406,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130041565</v>
+        <v>130041458</v>
       </c>
       <c r="B55" t="n">
-        <v>79087</v>
+        <v>79678</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6417,21 +6417,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>475456</v>
+        <v>475113</v>
       </c>
       <c r="R55" t="n">
-        <v>6832651</v>
+        <v>6832543</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6513,10 +6513,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130041596</v>
+        <v>130041449</v>
       </c>
       <c r="B56" t="n">
-        <v>79087</v>
+        <v>79120</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6524,21 +6524,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>475378</v>
+        <v>475100</v>
       </c>
       <c r="R56" t="n">
-        <v>6832576</v>
+        <v>6832696</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6620,10 +6620,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130041577</v>
+        <v>130041447</v>
       </c>
       <c r="B57" t="n">
-        <v>79087</v>
+        <v>79120</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6631,21 +6631,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>475162</v>
+        <v>475447</v>
       </c>
       <c r="R57" t="n">
-        <v>6832756</v>
+        <v>6832649</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6727,10 +6727,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130041498</v>
+        <v>130041450</v>
       </c>
       <c r="B58" t="n">
-        <v>78845</v>
+        <v>79120</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6738,21 +6738,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6762,10 +6762,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>475098</v>
+        <v>475269</v>
       </c>
       <c r="R58" t="n">
-        <v>6832700</v>
+        <v>6832659</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6837,7 +6837,7 @@
         <v>130041574</v>
       </c>
       <c r="B59" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6941,45 +6941,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130041443</v>
+        <v>130041462</v>
       </c>
       <c r="B60" t="n">
-        <v>79119</v>
+        <v>56930</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>475509</v>
+        <v>475321</v>
       </c>
       <c r="R60" t="n">
-        <v>6832511</v>
+        <v>6832648</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7011,7 +7016,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7021,7 +7026,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Under betad tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7048,32 +7058,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130041500</v>
+        <v>130041488</v>
       </c>
       <c r="B61" t="n">
-        <v>57844</v>
+        <v>78846</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7083,10 +7093,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>475142</v>
+        <v>475161</v>
       </c>
       <c r="R61" t="n">
-        <v>6832509</v>
+        <v>6832601</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7118,7 +7128,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7128,7 +7138,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7155,10 +7165,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130041598</v>
+        <v>130041443</v>
       </c>
       <c r="B62" t="n">
-        <v>79087</v>
+        <v>79120</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7166,21 +7176,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7190,10 +7200,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>475394</v>
+        <v>475509</v>
       </c>
       <c r="R62" t="n">
-        <v>6832587</v>
+        <v>6832511</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7225,7 +7235,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7235,7 +7245,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7262,10 +7272,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130041488</v>
+        <v>130041598</v>
       </c>
       <c r="B63" t="n">
-        <v>78845</v>
+        <v>79088</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7273,21 +7283,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7297,10 +7307,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>475161</v>
+        <v>475394</v>
       </c>
       <c r="R63" t="n">
-        <v>6832601</v>
+        <v>6832587</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7332,7 +7342,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7342,7 +7352,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7372,7 +7382,7 @@
         <v>130041566</v>
       </c>
       <c r="B64" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7476,10 +7486,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130041462</v>
+        <v>130041500</v>
       </c>
       <c r="B65" t="n">
-        <v>56930</v>
+        <v>57844</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7487,39 +7497,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>103031</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>475321</v>
+        <v>475142</v>
       </c>
       <c r="R65" t="n">
-        <v>6832648</v>
+        <v>6832509</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7551,7 +7556,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7561,12 +7566,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Under betad tall</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7596,7 +7596,7 @@
         <v>130041586</v>
       </c>
       <c r="B66" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7700,50 +7700,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130041463</v>
+        <v>130041568</v>
       </c>
       <c r="B67" t="n">
-        <v>56930</v>
+        <v>79088</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>475317</v>
+        <v>475381</v>
       </c>
       <c r="R67" t="n">
-        <v>6832770</v>
+        <v>6832661</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7775,7 +7770,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7785,12 +7780,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Under betad tall</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7817,10 +7807,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130041568</v>
+        <v>130041567</v>
       </c>
       <c r="B68" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7852,10 +7842,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>475381</v>
+        <v>475450</v>
       </c>
       <c r="R68" t="n">
-        <v>6832661</v>
+        <v>6832632</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7887,7 +7877,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7897,7 +7887,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7924,10 +7914,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130041567</v>
+        <v>130041563</v>
       </c>
       <c r="B69" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7959,10 +7949,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>475450</v>
+        <v>475527</v>
       </c>
       <c r="R69" t="n">
-        <v>6832632</v>
+        <v>6832623</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7994,7 +7984,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8004,7 +7994,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8031,10 +8021,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130041563</v>
+        <v>130041564</v>
       </c>
       <c r="B70" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8066,10 +8056,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>475527</v>
+        <v>475461</v>
       </c>
       <c r="R70" t="n">
-        <v>6832623</v>
+        <v>6832659</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8101,7 +8091,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8111,7 +8101,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8138,45 +8128,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130041564</v>
+        <v>130041463</v>
       </c>
       <c r="B71" t="n">
-        <v>79087</v>
+        <v>56930</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>475461</v>
+        <v>475317</v>
       </c>
       <c r="R71" t="n">
-        <v>6832659</v>
+        <v>6832770</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8208,7 +8203,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8218,7 +8213,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Under betad tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8245,38 +8245,38 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130041466</v>
+        <v>130041471</v>
       </c>
       <c r="B72" t="n">
-        <v>56930</v>
+        <v>57737</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>475445</v>
+        <v>475067</v>
       </c>
       <c r="R72" t="n">
-        <v>6832605</v>
+        <v>6832760</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8360,7 +8360,7 @@
         <v>130041528</v>
       </c>
       <c r="B73" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>130041589</v>
       </c>
       <c r="B74" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>130041542</v>
       </c>
       <c r="B75" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8678,38 +8678,38 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130041471</v>
+        <v>130041466</v>
       </c>
       <c r="B76" t="n">
-        <v>57737</v>
+        <v>56930</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8718,10 +8718,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>475067</v>
+        <v>475445</v>
       </c>
       <c r="R76" t="n">
-        <v>6832760</v>
+        <v>6832605</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8793,7 +8793,7 @@
         <v>130041523</v>
       </c>
       <c r="B77" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>130041580</v>
       </c>
       <c r="B78" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9001,6 +9001,1744 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>130044477</v>
+      </c>
+      <c r="B79" t="n">
+        <v>56930</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>475417</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6832617</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>130044550</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79088</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>475214</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6832713</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>130044472</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79088</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>475467</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6832594</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>130044543</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79088</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>475221</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6832703</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>130044494</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79678</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>475301</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6832730</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>3 hål,2 och 8 meter upp, diameter 3 och 6 cm</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>130044470</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79088</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>475494</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6832601</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>130044473</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>475417</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6832617</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>130044482</v>
+      </c>
+      <c r="B86" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>475342</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6832644</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>130044484</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79088</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>475322</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6832694</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>130044486</v>
+      </c>
+      <c r="B88" t="n">
+        <v>91606</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>475308</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6832714</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>130044552</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79707</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>475214</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6832713</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>130044501</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79088</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>475263</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6832664</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>130044481</v>
+      </c>
+      <c r="B91" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>475386</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6832591</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>130044571</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79088</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>475209</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6832640</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>130044565</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79088</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>475192</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6832673</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>130044480</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79088</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>475417</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6832617</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>130060248</v>
+      </c>
+      <c r="B95" t="n">
+        <v>78491</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>475301</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6832730</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54495-2025 artfynd.xlsx
+++ b/artfynd/A 54495-2025 artfynd.xlsx
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130041518</v>
+        <v>130041429</v>
       </c>
       <c r="B13" t="n">
-        <v>91620</v>
+        <v>79707</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475537</v>
+        <v>475441</v>
       </c>
       <c r="R13" t="n">
-        <v>6832616</v>
+        <v>6832541</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,12 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På kulturved (gammal timmerstomme)</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130041429</v>
+        <v>130041518</v>
       </c>
       <c r="B14" t="n">
-        <v>79707</v>
+        <v>91620</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2009,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475441</v>
+        <v>475537</v>
       </c>
       <c r="R14" t="n">
-        <v>6832541</v>
+        <v>6832616</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2049,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På kulturved (gammal timmerstomme)</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2835,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130041442</v>
+        <v>130041476</v>
       </c>
       <c r="B22" t="n">
-        <v>79707</v>
+        <v>57740</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2846,34 +2846,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475303</v>
+        <v>475245</v>
       </c>
       <c r="R22" t="n">
-        <v>6832754</v>
+        <v>6832734</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,7 +2910,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2920,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,38 +2952,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130041476</v>
+        <v>130041465</v>
       </c>
       <c r="B23" t="n">
-        <v>57740</v>
+        <v>56930</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2982,10 +2992,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475245</v>
+        <v>475430</v>
       </c>
       <c r="R23" t="n">
-        <v>6832734</v>
+        <v>6832587</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,7 +3027,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3027,12 +3037,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,50 +3064,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130041465</v>
+        <v>130041442</v>
       </c>
       <c r="B24" t="n">
-        <v>56930</v>
+        <v>79707</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475430</v>
+        <v>475303</v>
       </c>
       <c r="R24" t="n">
-        <v>6832587</v>
+        <v>6832754</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -5112,7 +5112,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130041529</v>
+        <v>130041588</v>
       </c>
       <c r="B43" t="n">
         <v>79088</v>
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>475095</v>
+        <v>475058</v>
       </c>
       <c r="R43" t="n">
-        <v>6832582</v>
+        <v>6832696</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5182,7 +5182,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5219,7 +5219,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130041583</v>
+        <v>130041571</v>
       </c>
       <c r="B44" t="n">
         <v>79088</v>
@@ -5254,10 +5254,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475057</v>
+        <v>475307</v>
       </c>
       <c r="R44" t="n">
-        <v>6832751</v>
+        <v>6832773</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5326,7 +5326,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130041575</v>
+        <v>130041529</v>
       </c>
       <c r="B45" t="n">
         <v>79088</v>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>475266</v>
+        <v>475095</v>
       </c>
       <c r="R45" t="n">
-        <v>6832803</v>
+        <v>6832582</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5433,7 +5433,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130041588</v>
+        <v>130041583</v>
       </c>
       <c r="B46" t="n">
         <v>79088</v>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475058</v>
+        <v>475057</v>
       </c>
       <c r="R46" t="n">
-        <v>6832696</v>
+        <v>6832751</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5540,10 +5540,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130041571</v>
+        <v>130041475</v>
       </c>
       <c r="B47" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5551,34 +5551,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>475307</v>
+        <v>475277</v>
       </c>
       <c r="R47" t="n">
-        <v>6832773</v>
+        <v>6832740</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5610,7 +5615,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5620,7 +5625,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran), högst 5 år gamla</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5647,10 +5657,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130041475</v>
+        <v>130041575</v>
       </c>
       <c r="B48" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5658,39 +5668,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>475277</v>
+        <v>475266</v>
       </c>
       <c r="R48" t="n">
-        <v>6832740</v>
+        <v>6832803</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5722,7 +5727,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5732,12 +5737,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran), högst 5 år gamla</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7700,7 +7700,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130041568</v>
+        <v>130041563</v>
       </c>
       <c r="B67" t="n">
         <v>79088</v>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>475381</v>
+        <v>475527</v>
       </c>
       <c r="R67" t="n">
-        <v>6832661</v>
+        <v>6832623</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7807,7 +7807,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130041567</v>
+        <v>130041564</v>
       </c>
       <c r="B68" t="n">
         <v>79088</v>
@@ -7842,10 +7842,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>475450</v>
+        <v>475461</v>
       </c>
       <c r="R68" t="n">
-        <v>6832632</v>
+        <v>6832659</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7877,7 +7877,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7914,45 +7914,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130041563</v>
+        <v>130041463</v>
       </c>
       <c r="B69" t="n">
-        <v>79088</v>
+        <v>56930</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>475527</v>
+        <v>475317</v>
       </c>
       <c r="R69" t="n">
-        <v>6832623</v>
+        <v>6832770</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7984,7 +7989,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7994,7 +7999,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Under betad tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8021,7 +8031,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130041564</v>
+        <v>130041568</v>
       </c>
       <c r="B70" t="n">
         <v>79088</v>
@@ -8056,10 +8066,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>475461</v>
+        <v>475381</v>
       </c>
       <c r="R70" t="n">
-        <v>6832659</v>
+        <v>6832661</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8091,7 +8101,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8101,7 +8111,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8128,50 +8138,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130041463</v>
+        <v>130041567</v>
       </c>
       <c r="B71" t="n">
-        <v>56930</v>
+        <v>79088</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>475317</v>
+        <v>475450</v>
       </c>
       <c r="R71" t="n">
-        <v>6832770</v>
+        <v>6832632</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8203,7 +8208,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8213,12 +8218,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Under betad tall</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 54495-2025 artfynd.xlsx
+++ b/artfynd/A 54495-2025 artfynd.xlsx
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130041429</v>
+        <v>130041518</v>
       </c>
       <c r="B13" t="n">
-        <v>79707</v>
+        <v>91620</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475441</v>
+        <v>475537</v>
       </c>
       <c r="R13" t="n">
-        <v>6832541</v>
+        <v>6832616</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På kulturved (gammal timmerstomme)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130041518</v>
+        <v>130041429</v>
       </c>
       <c r="B14" t="n">
-        <v>91620</v>
+        <v>79707</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,21 +1985,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475537</v>
+        <v>475441</v>
       </c>
       <c r="R14" t="n">
-        <v>6832616</v>
+        <v>6832541</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,12 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På kulturved (gammal timmerstomme)</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2835,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130041476</v>
+        <v>130041442</v>
       </c>
       <c r="B22" t="n">
-        <v>57740</v>
+        <v>79707</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2846,39 +2846,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475245</v>
+        <v>475303</v>
       </c>
       <c r="R22" t="n">
-        <v>6832734</v>
+        <v>6832754</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2920,12 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,38 +2942,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130041465</v>
+        <v>130041476</v>
       </c>
       <c r="B23" t="n">
-        <v>56930</v>
+        <v>57740</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2992,10 +2982,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475430</v>
+        <v>475245</v>
       </c>
       <c r="R23" t="n">
-        <v>6832587</v>
+        <v>6832734</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3027,7 +3017,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3037,7 +3027,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3064,45 +3059,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130041442</v>
+        <v>130041465</v>
       </c>
       <c r="B24" t="n">
-        <v>79707</v>
+        <v>56930</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475303</v>
+        <v>475430</v>
       </c>
       <c r="R24" t="n">
-        <v>6832754</v>
+        <v>6832587</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -5112,7 +5112,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130041588</v>
+        <v>130041529</v>
       </c>
       <c r="B43" t="n">
         <v>79088</v>
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>475058</v>
+        <v>475095</v>
       </c>
       <c r="R43" t="n">
-        <v>6832696</v>
+        <v>6832582</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5182,7 +5182,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5219,7 +5219,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130041571</v>
+        <v>130041583</v>
       </c>
       <c r="B44" t="n">
         <v>79088</v>
@@ -5254,10 +5254,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475307</v>
+        <v>475057</v>
       </c>
       <c r="R44" t="n">
-        <v>6832773</v>
+        <v>6832751</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5326,7 +5326,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130041529</v>
+        <v>130041575</v>
       </c>
       <c r="B45" t="n">
         <v>79088</v>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>475095</v>
+        <v>475266</v>
       </c>
       <c r="R45" t="n">
-        <v>6832582</v>
+        <v>6832803</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5433,7 +5433,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130041583</v>
+        <v>130041588</v>
       </c>
       <c r="B46" t="n">
         <v>79088</v>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475057</v>
+        <v>475058</v>
       </c>
       <c r="R46" t="n">
-        <v>6832751</v>
+        <v>6832696</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5540,10 +5540,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130041475</v>
+        <v>130041571</v>
       </c>
       <c r="B47" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5551,39 +5551,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>475277</v>
+        <v>475307</v>
       </c>
       <c r="R47" t="n">
-        <v>6832740</v>
+        <v>6832773</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5615,7 +5610,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5625,12 +5620,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran), högst 5 år gamla</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5657,10 +5647,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130041575</v>
+        <v>130041475</v>
       </c>
       <c r="B48" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5668,34 +5658,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>475266</v>
+        <v>475277</v>
       </c>
       <c r="R48" t="n">
-        <v>6832803</v>
+        <v>6832740</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5727,7 +5722,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5737,7 +5732,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran), högst 5 år gamla</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5764,10 +5764,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130041570</v>
+        <v>130041449</v>
       </c>
       <c r="B49" t="n">
-        <v>79088</v>
+        <v>79120</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5775,21 +5775,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>475287</v>
+        <v>475100</v>
       </c>
       <c r="R49" t="n">
-        <v>6832747</v>
+        <v>6832696</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5871,32 +5871,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130041482</v>
+        <v>130041447</v>
       </c>
       <c r="B50" t="n">
-        <v>79112</v>
+        <v>79120</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6434</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>475500</v>
+        <v>475447</v>
       </c>
       <c r="R50" t="n">
-        <v>6832632</v>
+        <v>6832649</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5978,10 +5978,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130041565</v>
+        <v>130041450</v>
       </c>
       <c r="B51" t="n">
-        <v>79088</v>
+        <v>79120</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5989,21 +5989,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>475456</v>
+        <v>475269</v>
       </c>
       <c r="R51" t="n">
-        <v>6832651</v>
+        <v>6832659</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6085,32 +6085,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130041596</v>
+        <v>130041482</v>
       </c>
       <c r="B52" t="n">
-        <v>79088</v>
+        <v>79112</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>475378</v>
+        <v>475500</v>
       </c>
       <c r="R52" t="n">
-        <v>6832576</v>
+        <v>6832632</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6192,7 +6192,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130041577</v>
+        <v>130041565</v>
       </c>
       <c r="B53" t="n">
         <v>79088</v>
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>475162</v>
+        <v>475456</v>
       </c>
       <c r="R53" t="n">
-        <v>6832756</v>
+        <v>6832651</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6406,10 +6406,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130041458</v>
+        <v>130041570</v>
       </c>
       <c r="B55" t="n">
-        <v>79678</v>
+        <v>79088</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6417,21 +6417,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>475113</v>
+        <v>475287</v>
       </c>
       <c r="R55" t="n">
-        <v>6832543</v>
+        <v>6832747</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6513,10 +6513,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130041449</v>
+        <v>130041596</v>
       </c>
       <c r="B56" t="n">
-        <v>79120</v>
+        <v>79088</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6524,21 +6524,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>475100</v>
+        <v>475378</v>
       </c>
       <c r="R56" t="n">
-        <v>6832696</v>
+        <v>6832576</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6620,10 +6620,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130041447</v>
+        <v>130041577</v>
       </c>
       <c r="B57" t="n">
-        <v>79120</v>
+        <v>79088</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6631,21 +6631,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>475447</v>
+        <v>475162</v>
       </c>
       <c r="R57" t="n">
-        <v>6832649</v>
+        <v>6832756</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6727,10 +6727,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130041450</v>
+        <v>130041458</v>
       </c>
       <c r="B58" t="n">
-        <v>79120</v>
+        <v>79678</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6738,21 +6738,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6762,10 +6762,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>475269</v>
+        <v>475113</v>
       </c>
       <c r="R58" t="n">
-        <v>6832659</v>
+        <v>6832543</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7700,45 +7700,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130041563</v>
+        <v>130041463</v>
       </c>
       <c r="B67" t="n">
-        <v>79088</v>
+        <v>56930</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>475527</v>
+        <v>475317</v>
       </c>
       <c r="R67" t="n">
-        <v>6832623</v>
+        <v>6832770</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7770,7 +7775,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7780,7 +7785,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Under betad tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7807,7 +7817,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130041564</v>
+        <v>130041568</v>
       </c>
       <c r="B68" t="n">
         <v>79088</v>
@@ -7842,10 +7852,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>475461</v>
+        <v>475381</v>
       </c>
       <c r="R68" t="n">
-        <v>6832659</v>
+        <v>6832661</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7877,7 +7887,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7887,7 +7897,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7914,50 +7924,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130041463</v>
+        <v>130041567</v>
       </c>
       <c r="B69" t="n">
-        <v>56930</v>
+        <v>79088</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>475317</v>
+        <v>475450</v>
       </c>
       <c r="R69" t="n">
-        <v>6832770</v>
+        <v>6832632</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7989,7 +7994,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7999,12 +8004,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Under betad tall</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8031,7 +8031,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130041568</v>
+        <v>130041563</v>
       </c>
       <c r="B70" t="n">
         <v>79088</v>
@@ -8066,10 +8066,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>475381</v>
+        <v>475527</v>
       </c>
       <c r="R70" t="n">
-        <v>6832661</v>
+        <v>6832623</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8138,7 +8138,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130041567</v>
+        <v>130041564</v>
       </c>
       <c r="B71" t="n">
         <v>79088</v>
@@ -8173,10 +8173,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>475450</v>
+        <v>475461</v>
       </c>
       <c r="R71" t="n">
-        <v>6832632</v>
+        <v>6832659</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 54495-2025 artfynd.xlsx
+++ b/artfynd/A 54495-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130041585</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130041599</v>
       </c>
       <c r="B3" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130041502</v>
       </c>
       <c r="B4" t="n">
-        <v>81073</v>
+        <v>81074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130041525</v>
+        <v>130041582</v>
       </c>
       <c r="B5" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475108</v>
+        <v>475060</v>
       </c>
       <c r="R5" t="n">
-        <v>6832521</v>
+        <v>6832756</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130041582</v>
+        <v>130041525</v>
       </c>
       <c r="B6" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475060</v>
+        <v>475108</v>
       </c>
       <c r="R6" t="n">
-        <v>6832756</v>
+        <v>6832521</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,7 +1213,7 @@
         <v>130041579</v>
       </c>
       <c r="B7" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130041603</v>
+        <v>130041518</v>
       </c>
       <c r="B9" t="n">
-        <v>78754</v>
+        <v>91637</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475161</v>
+        <v>475537</v>
       </c>
       <c r="R9" t="n">
-        <v>6832599</v>
+        <v>6832616</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På kulturved (gammal timmerstomme)</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130041595</v>
+        <v>130041603</v>
       </c>
       <c r="B10" t="n">
-        <v>79088</v>
+        <v>78755</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1557,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475334</v>
+        <v>475161</v>
       </c>
       <c r="R10" t="n">
-        <v>6832589</v>
+        <v>6832599</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130041578</v>
+        <v>130041429</v>
       </c>
       <c r="B11" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,21 +1664,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475123</v>
+        <v>475441</v>
       </c>
       <c r="R11" t="n">
-        <v>6832763</v>
+        <v>6832541</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130041527</v>
+        <v>130041578</v>
       </c>
       <c r="B12" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475061</v>
+        <v>475123</v>
       </c>
       <c r="R12" t="n">
-        <v>6832499</v>
+        <v>6832763</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1830,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1840,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130041518</v>
+        <v>130041527</v>
       </c>
       <c r="B13" t="n">
-        <v>91620</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1878,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475537</v>
+        <v>475061</v>
       </c>
       <c r="R13" t="n">
-        <v>6832616</v>
+        <v>6832499</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,12 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På kulturved (gammal timmerstomme)</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130041429</v>
+        <v>130041595</v>
       </c>
       <c r="B14" t="n">
-        <v>79707</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,21 +1985,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475441</v>
+        <v>475334</v>
       </c>
       <c r="R14" t="n">
-        <v>6832541</v>
+        <v>6832589</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,7 +2084,7 @@
         <v>130041592</v>
       </c>
       <c r="B15" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130041593</v>
+        <v>130041522</v>
       </c>
       <c r="B16" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475269</v>
+        <v>475323</v>
       </c>
       <c r="R16" t="n">
-        <v>6832659</v>
+        <v>6832544</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,45 +2295,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130041522</v>
+        <v>130041464</v>
       </c>
       <c r="B17" t="n">
-        <v>79088</v>
+        <v>56930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475323</v>
+        <v>475156</v>
       </c>
       <c r="R17" t="n">
-        <v>6832544</v>
+        <v>6832751</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,50 +2407,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130041464</v>
+        <v>130041593</v>
       </c>
       <c r="B18" t="n">
-        <v>56930</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475156</v>
+        <v>475269</v>
       </c>
       <c r="R18" t="n">
-        <v>6832751</v>
+        <v>6832659</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,32 +2514,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130041483</v>
+        <v>130041597</v>
       </c>
       <c r="B19" t="n">
-        <v>79112</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475269</v>
+        <v>475391</v>
       </c>
       <c r="R19" t="n">
-        <v>6832659</v>
+        <v>6832581</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130041597</v>
+        <v>130041543</v>
       </c>
       <c r="B20" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475391</v>
+        <v>475124</v>
       </c>
       <c r="R20" t="n">
-        <v>6832581</v>
+        <v>6832639</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,45 +2728,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130041543</v>
+        <v>130041465</v>
       </c>
       <c r="B21" t="n">
-        <v>79088</v>
+        <v>56930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475124</v>
+        <v>475430</v>
       </c>
       <c r="R21" t="n">
-        <v>6832639</v>
+        <v>6832587</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2798,7 +2803,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2808,7 +2813,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,32 +2840,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130041442</v>
+        <v>130041483</v>
       </c>
       <c r="B22" t="n">
-        <v>79707</v>
+        <v>79113</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475303</v>
+        <v>475269</v>
       </c>
       <c r="R22" t="n">
-        <v>6832754</v>
+        <v>6832659</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,7 +2910,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2920,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,10 +2947,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130041476</v>
+        <v>130041442</v>
       </c>
       <c r="B23" t="n">
-        <v>57740</v>
+        <v>79708</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2953,39 +2958,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475245</v>
+        <v>475303</v>
       </c>
       <c r="R23" t="n">
-        <v>6832734</v>
+        <v>6832754</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3027,12 +3027,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,38 +3054,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130041465</v>
+        <v>130041476</v>
       </c>
       <c r="B24" t="n">
-        <v>56930</v>
+        <v>57740</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3099,10 +3094,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475430</v>
+        <v>475245</v>
       </c>
       <c r="R24" t="n">
-        <v>6832587</v>
+        <v>6832734</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3134,7 +3129,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3144,7 +3139,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3171,10 +3171,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130041590</v>
+        <v>130041572</v>
       </c>
       <c r="B25" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475119</v>
+        <v>475301</v>
       </c>
       <c r="R25" t="n">
-        <v>6832699</v>
+        <v>6832783</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3278,10 +3278,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130041572</v>
+        <v>130041608</v>
       </c>
       <c r="B26" t="n">
-        <v>79088</v>
+        <v>78492</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,21 +3289,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475301</v>
+        <v>475113</v>
       </c>
       <c r="R26" t="n">
-        <v>6832783</v>
+        <v>6832544</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3385,10 +3385,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130041608</v>
+        <v>130041590</v>
       </c>
       <c r="B27" t="n">
-        <v>78491</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,21 +3396,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>475113</v>
+        <v>475119</v>
       </c>
       <c r="R27" t="n">
-        <v>6832544</v>
+        <v>6832699</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3604,10 +3604,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130041448</v>
+        <v>130041573</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3615,21 +3615,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>475341</v>
+        <v>475283</v>
       </c>
       <c r="R29" t="n">
-        <v>6832665</v>
+        <v>6832815</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3711,10 +3711,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130041573</v>
+        <v>130041473</v>
       </c>
       <c r="B30" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3722,34 +3722,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>475283</v>
+        <v>475044</v>
       </c>
       <c r="R30" t="n">
-        <v>6832815</v>
+        <v>6832743</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3781,7 +3786,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3791,7 +3796,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3821,7 +3831,7 @@
         <v>130041584</v>
       </c>
       <c r="B31" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3925,10 +3935,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130041473</v>
+        <v>130041448</v>
       </c>
       <c r="B32" t="n">
-        <v>57740</v>
+        <v>79121</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3936,39 +3946,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>475044</v>
+        <v>475341</v>
       </c>
       <c r="R32" t="n">
-        <v>6832743</v>
+        <v>6832665</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4000,7 +4005,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4010,12 +4015,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4045,7 +4045,7 @@
         <v>130041602</v>
       </c>
       <c r="B33" t="n">
-        <v>78754</v>
+        <v>78755</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>130041591</v>
       </c>
       <c r="B34" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>130041544</v>
       </c>
       <c r="B35" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4363,10 +4363,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130041524</v>
+        <v>130041430</v>
       </c>
       <c r="B36" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4374,21 +4374,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>475144</v>
+        <v>475161</v>
       </c>
       <c r="R36" t="n">
-        <v>6832586</v>
+        <v>6832599</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4470,10 +4470,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130041430</v>
+        <v>130041524</v>
       </c>
       <c r="B37" t="n">
-        <v>79707</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>475161</v>
+        <v>475144</v>
       </c>
       <c r="R37" t="n">
-        <v>6832599</v>
+        <v>6832586</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4577,10 +4577,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130041594</v>
+        <v>130041576</v>
       </c>
       <c r="B38" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>475287</v>
+        <v>475266</v>
       </c>
       <c r="R38" t="n">
-        <v>6832631</v>
+        <v>6832776</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4684,10 +4684,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130041600</v>
+        <v>130041562</v>
       </c>
       <c r="B39" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>475471</v>
+        <v>475531</v>
       </c>
       <c r="R39" t="n">
-        <v>6832571</v>
+        <v>6832619</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4791,10 +4791,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130041562</v>
+        <v>130041526</v>
       </c>
       <c r="B40" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>475531</v>
+        <v>475142</v>
       </c>
       <c r="R40" t="n">
-        <v>6832619</v>
+        <v>6832509</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4898,10 +4898,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130041576</v>
+        <v>130041594</v>
       </c>
       <c r="B41" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>475266</v>
+        <v>475287</v>
       </c>
       <c r="R41" t="n">
-        <v>6832776</v>
+        <v>6832631</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5005,10 +5005,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130041526</v>
+        <v>130041600</v>
       </c>
       <c r="B42" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5040,10 +5040,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>475142</v>
+        <v>475471</v>
       </c>
       <c r="R42" t="n">
-        <v>6832509</v>
+        <v>6832571</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5112,10 +5112,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130041529</v>
+        <v>130041588</v>
       </c>
       <c r="B43" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>475095</v>
+        <v>475058</v>
       </c>
       <c r="R43" t="n">
-        <v>6832582</v>
+        <v>6832696</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5182,7 +5182,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5219,10 +5219,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130041583</v>
+        <v>130041575</v>
       </c>
       <c r="B44" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5254,10 +5254,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475057</v>
+        <v>475266</v>
       </c>
       <c r="R44" t="n">
-        <v>6832751</v>
+        <v>6832803</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5326,10 +5326,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130041575</v>
+        <v>130041571</v>
       </c>
       <c r="B45" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>475266</v>
+        <v>475307</v>
       </c>
       <c r="R45" t="n">
-        <v>6832803</v>
+        <v>6832773</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5433,10 +5433,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130041588</v>
+        <v>130041529</v>
       </c>
       <c r="B46" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475058</v>
+        <v>475095</v>
       </c>
       <c r="R46" t="n">
-        <v>6832696</v>
+        <v>6832582</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5540,10 +5540,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130041571</v>
+        <v>130041583</v>
       </c>
       <c r="B47" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>475307</v>
+        <v>475057</v>
       </c>
       <c r="R47" t="n">
-        <v>6832773</v>
+        <v>6832751</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5764,32 +5764,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130041449</v>
+        <v>130041482</v>
       </c>
       <c r="B49" t="n">
-        <v>79120</v>
+        <v>79113</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6434</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>475100</v>
+        <v>475500</v>
       </c>
       <c r="R49" t="n">
-        <v>6832696</v>
+        <v>6832632</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5871,10 +5871,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130041447</v>
+        <v>130041450</v>
       </c>
       <c r="B50" t="n">
-        <v>79120</v>
+        <v>79121</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>475447</v>
+        <v>475269</v>
       </c>
       <c r="R50" t="n">
-        <v>6832649</v>
+        <v>6832659</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5978,10 +5978,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130041450</v>
+        <v>130041447</v>
       </c>
       <c r="B51" t="n">
-        <v>79120</v>
+        <v>79121</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>475269</v>
+        <v>475447</v>
       </c>
       <c r="R51" t="n">
-        <v>6832659</v>
+        <v>6832649</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6085,32 +6085,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130041482</v>
+        <v>130041449</v>
       </c>
       <c r="B52" t="n">
-        <v>79112</v>
+        <v>79121</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6434</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>475500</v>
+        <v>475100</v>
       </c>
       <c r="R52" t="n">
-        <v>6832632</v>
+        <v>6832696</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6192,10 +6192,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130041565</v>
+        <v>130041570</v>
       </c>
       <c r="B53" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>475456</v>
+        <v>475287</v>
       </c>
       <c r="R53" t="n">
-        <v>6832651</v>
+        <v>6832747</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6299,10 +6299,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130041498</v>
+        <v>130041565</v>
       </c>
       <c r="B54" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6310,21 +6310,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>475098</v>
+        <v>475456</v>
       </c>
       <c r="R54" t="n">
-        <v>6832700</v>
+        <v>6832651</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6406,10 +6406,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130041570</v>
+        <v>130041596</v>
       </c>
       <c r="B55" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>475287</v>
+        <v>475378</v>
       </c>
       <c r="R55" t="n">
-        <v>6832747</v>
+        <v>6832576</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6513,10 +6513,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130041596</v>
+        <v>130041577</v>
       </c>
       <c r="B56" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>475378</v>
+        <v>475162</v>
       </c>
       <c r="R56" t="n">
-        <v>6832576</v>
+        <v>6832756</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6620,10 +6620,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130041577</v>
+        <v>130041458</v>
       </c>
       <c r="B57" t="n">
-        <v>79088</v>
+        <v>79679</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6631,21 +6631,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>475162</v>
+        <v>475113</v>
       </c>
       <c r="R57" t="n">
-        <v>6832756</v>
+        <v>6832543</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6727,10 +6727,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130041458</v>
+        <v>130041498</v>
       </c>
       <c r="B58" t="n">
-        <v>79678</v>
+        <v>78847</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6738,21 +6738,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6762,10 +6762,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>475113</v>
+        <v>475098</v>
       </c>
       <c r="R58" t="n">
-        <v>6832543</v>
+        <v>6832700</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6837,7 +6837,7 @@
         <v>130041574</v>
       </c>
       <c r="B59" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6941,50 +6941,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130041462</v>
+        <v>130041443</v>
       </c>
       <c r="B60" t="n">
-        <v>56930</v>
+        <v>79121</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>475321</v>
+        <v>475509</v>
       </c>
       <c r="R60" t="n">
-        <v>6832648</v>
+        <v>6832511</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7016,7 +7011,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7026,12 +7021,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Under betad tall</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7061,7 +7051,7 @@
         <v>130041488</v>
       </c>
       <c r="B61" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7165,10 +7155,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130041443</v>
+        <v>130041598</v>
       </c>
       <c r="B62" t="n">
-        <v>79120</v>
+        <v>79089</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7176,21 +7166,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7200,10 +7190,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>475509</v>
+        <v>475394</v>
       </c>
       <c r="R62" t="n">
-        <v>6832511</v>
+        <v>6832587</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7235,7 +7225,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7245,7 +7235,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7272,10 +7262,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130041598</v>
+        <v>130041566</v>
       </c>
       <c r="B63" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7307,10 +7297,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>475394</v>
+        <v>475443</v>
       </c>
       <c r="R63" t="n">
-        <v>6832587</v>
+        <v>6832633</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7342,7 +7332,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7352,7 +7342,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7379,45 +7369,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130041566</v>
+        <v>130041462</v>
       </c>
       <c r="B64" t="n">
-        <v>79088</v>
+        <v>56930</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>475443</v>
+        <v>475321</v>
       </c>
       <c r="R64" t="n">
-        <v>6832633</v>
+        <v>6832648</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7449,7 +7444,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7459,7 +7454,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Under betad tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7596,7 +7596,7 @@
         <v>130041586</v>
       </c>
       <c r="B66" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7700,50 +7700,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130041463</v>
+        <v>130041567</v>
       </c>
       <c r="B67" t="n">
-        <v>56930</v>
+        <v>79089</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>475317</v>
+        <v>475450</v>
       </c>
       <c r="R67" t="n">
-        <v>6832770</v>
+        <v>6832632</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7775,7 +7770,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7785,12 +7780,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Under betad tall</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7817,10 +7807,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130041568</v>
+        <v>130041563</v>
       </c>
       <c r="B68" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7852,10 +7842,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>475381</v>
+        <v>475527</v>
       </c>
       <c r="R68" t="n">
-        <v>6832661</v>
+        <v>6832623</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7887,7 +7877,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7897,7 +7887,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7924,10 +7914,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130041567</v>
+        <v>130041568</v>
       </c>
       <c r="B69" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7959,10 +7949,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>475450</v>
+        <v>475381</v>
       </c>
       <c r="R69" t="n">
-        <v>6832632</v>
+        <v>6832661</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7994,7 +7984,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8004,7 +7994,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8031,10 +8021,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130041563</v>
+        <v>130041564</v>
       </c>
       <c r="B70" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8066,10 +8056,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>475527</v>
+        <v>475461</v>
       </c>
       <c r="R70" t="n">
-        <v>6832623</v>
+        <v>6832659</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8101,7 +8091,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8111,7 +8101,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8138,45 +8128,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130041564</v>
+        <v>130041463</v>
       </c>
       <c r="B71" t="n">
-        <v>79088</v>
+        <v>56930</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>475461</v>
+        <v>475317</v>
       </c>
       <c r="R71" t="n">
-        <v>6832659</v>
+        <v>6832770</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8208,7 +8203,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8218,7 +8213,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Under betad tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8245,10 +8245,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130041471</v>
+        <v>130041589</v>
       </c>
       <c r="B72" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8256,39 +8256,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>475067</v>
+        <v>475077</v>
       </c>
       <c r="R72" t="n">
-        <v>6832760</v>
+        <v>6832687</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8320,7 +8315,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8330,7 +8325,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8357,10 +8352,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130041528</v>
+        <v>130041542</v>
       </c>
       <c r="B73" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8392,10 +8387,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>475072</v>
+        <v>475107</v>
       </c>
       <c r="R73" t="n">
-        <v>6832555</v>
+        <v>6832635</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8427,7 +8422,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8437,7 +8432,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8464,10 +8459,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130041589</v>
+        <v>130041528</v>
       </c>
       <c r="B74" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8499,10 +8494,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>475077</v>
+        <v>475072</v>
       </c>
       <c r="R74" t="n">
-        <v>6832687</v>
+        <v>6832555</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8534,7 +8529,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8544,7 +8539,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8571,10 +8566,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130041542</v>
+        <v>130041471</v>
       </c>
       <c r="B75" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8582,34 +8577,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>475107</v>
+        <v>475067</v>
       </c>
       <c r="R75" t="n">
-        <v>6832635</v>
+        <v>6832760</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8793,7 +8793,7 @@
         <v>130041523</v>
       </c>
       <c r="B77" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>130041580</v>
       </c>
       <c r="B78" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9004,42 +9004,37 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130044477</v>
+        <v>130044550</v>
       </c>
       <c r="B79" t="n">
-        <v>56930</v>
+        <v>79089</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9047,10 +9042,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>475417</v>
+        <v>475214</v>
       </c>
       <c r="R79" t="n">
-        <v>6832617</v>
+        <v>6832713</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9091,6 +9086,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9109,37 +9105,42 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130044550</v>
+        <v>130044477</v>
       </c>
       <c r="B80" t="n">
-        <v>79088</v>
+        <v>56930</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9147,10 +9148,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>475214</v>
+        <v>475417</v>
       </c>
       <c r="R80" t="n">
-        <v>6832713</v>
+        <v>6832617</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9191,7 +9192,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9213,7 +9213,7 @@
         <v>130044472</v>
       </c>
       <c r="B81" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>130044543</v>
       </c>
       <c r="B82" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>130044494</v>
       </c>
       <c r="B83" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>130044470</v>
       </c>
       <c r="B84" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>130044484</v>
       </c>
       <c r="B87" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>130044486</v>
       </c>
       <c r="B88" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>130044552</v>
       </c>
       <c r="B89" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>130044501</v>
       </c>
       <c r="B90" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10233,10 +10233,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130044481</v>
+        <v>130044571</v>
       </c>
       <c r="B91" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10244,31 +10244,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10276,10 +10271,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>475386</v>
+        <v>475209</v>
       </c>
       <c r="R91" t="n">
-        <v>6832591</v>
+        <v>6832640</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10320,6 +10315,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10338,10 +10334,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130044571</v>
+        <v>130044481</v>
       </c>
       <c r="B92" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10349,26 +10345,31 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -10376,10 +10377,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>475209</v>
+        <v>475386</v>
       </c>
       <c r="R92" t="n">
-        <v>6832640</v>
+        <v>6832591</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10420,7 +10421,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10442,7 +10442,7 @@
         <v>130044565</v>
       </c>
       <c r="B93" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>130044480</v>
       </c>
       <c r="B94" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>130060248</v>
       </c>
       <c r="B95" t="n">
-        <v>78491</v>
+        <v>78492</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 54495-2025 artfynd.xlsx
+++ b/artfynd/A 54495-2025 artfynd.xlsx
@@ -2081,50 +2081,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130041464</v>
+        <v>130041592</v>
       </c>
       <c r="B15" t="n">
-        <v>56931</v>
+        <v>79095</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475156</v>
+        <v>475196</v>
       </c>
       <c r="R15" t="n">
-        <v>6832751</v>
+        <v>6832709</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,7 +2188,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130041592</v>
+        <v>130041593</v>
       </c>
       <c r="B16" t="n">
         <v>79095</v>
@@ -2228,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475196</v>
+        <v>475269</v>
       </c>
       <c r="R16" t="n">
-        <v>6832709</v>
+        <v>6832659</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,7 +2295,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130041593</v>
+        <v>130041522</v>
       </c>
       <c r="B17" t="n">
         <v>79095</v>
@@ -2335,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475269</v>
+        <v>475323</v>
       </c>
       <c r="R17" t="n">
-        <v>6832659</v>
+        <v>6832544</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,45 +2402,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130041522</v>
+        <v>130041464</v>
       </c>
       <c r="B18" t="n">
-        <v>79095</v>
+        <v>56931</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475323</v>
+        <v>475156</v>
       </c>
       <c r="R18" t="n">
-        <v>6832544</v>
+        <v>6832751</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -4363,10 +4363,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130041430</v>
+        <v>130041524</v>
       </c>
       <c r="B36" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4374,21 +4374,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>475161</v>
+        <v>475144</v>
       </c>
       <c r="R36" t="n">
-        <v>6832599</v>
+        <v>6832586</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4470,10 +4470,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130041524</v>
+        <v>130041430</v>
       </c>
       <c r="B37" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>475144</v>
+        <v>475161</v>
       </c>
       <c r="R37" t="n">
-        <v>6832586</v>
+        <v>6832599</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -6085,10 +6085,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130041458</v>
+        <v>130041570</v>
       </c>
       <c r="B52" t="n">
-        <v>79685</v>
+        <v>79095</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6096,21 +6096,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>475113</v>
+        <v>475287</v>
       </c>
       <c r="R52" t="n">
-        <v>6832543</v>
+        <v>6832747</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6192,32 +6192,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130041498</v>
+        <v>130041482</v>
       </c>
       <c r="B53" t="n">
-        <v>78853</v>
+        <v>79119</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>475098</v>
+        <v>475500</v>
       </c>
       <c r="R53" t="n">
-        <v>6832700</v>
+        <v>6832632</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6299,7 +6299,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130041570</v>
+        <v>130041565</v>
       </c>
       <c r="B54" t="n">
         <v>79095</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>475287</v>
+        <v>475456</v>
       </c>
       <c r="R54" t="n">
-        <v>6832747</v>
+        <v>6832651</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6406,32 +6406,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130041482</v>
+        <v>130041596</v>
       </c>
       <c r="B55" t="n">
-        <v>79119</v>
+        <v>79095</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>475500</v>
+        <v>475378</v>
       </c>
       <c r="R55" t="n">
-        <v>6832632</v>
+        <v>6832576</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6513,7 +6513,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130041565</v>
+        <v>130041577</v>
       </c>
       <c r="B56" t="n">
         <v>79095</v>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>475456</v>
+        <v>475162</v>
       </c>
       <c r="R56" t="n">
-        <v>6832651</v>
+        <v>6832756</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6620,10 +6620,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130041596</v>
+        <v>130041458</v>
       </c>
       <c r="B57" t="n">
-        <v>79095</v>
+        <v>79685</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6631,21 +6631,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>475378</v>
+        <v>475113</v>
       </c>
       <c r="R57" t="n">
-        <v>6832576</v>
+        <v>6832543</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6727,10 +6727,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130041577</v>
+        <v>130041498</v>
       </c>
       <c r="B58" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6738,21 +6738,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6762,10 +6762,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>475162</v>
+        <v>475098</v>
       </c>
       <c r="R58" t="n">
-        <v>6832756</v>
+        <v>6832700</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -9518,10 +9518,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130044470</v>
+        <v>130044473</v>
       </c>
       <c r="B84" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9529,26 +9529,31 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9556,10 +9561,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>475494</v>
+        <v>475417</v>
       </c>
       <c r="R84" t="n">
-        <v>6832601</v>
+        <v>6832617</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9600,7 +9605,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9619,10 +9623,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130044473</v>
+        <v>130044470</v>
       </c>
       <c r="B85" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9630,31 +9634,26 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -9662,10 +9661,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>475417</v>
+        <v>475494</v>
       </c>
       <c r="R85" t="n">
-        <v>6832617</v>
+        <v>6832601</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9706,6 +9705,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10233,10 +10233,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130044481</v>
+        <v>130044571</v>
       </c>
       <c r="B91" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10244,31 +10244,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10276,10 +10271,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>475386</v>
+        <v>475209</v>
       </c>
       <c r="R91" t="n">
-        <v>6832591</v>
+        <v>6832640</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10320,6 +10315,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10338,10 +10334,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130044571</v>
+        <v>130044481</v>
       </c>
       <c r="B92" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10349,26 +10345,31 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -10376,10 +10377,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>475209</v>
+        <v>475386</v>
       </c>
       <c r="R92" t="n">
-        <v>6832640</v>
+        <v>6832591</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10420,7 +10421,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54495-2025 artfynd.xlsx
+++ b/artfynd/A 54495-2025 artfynd.xlsx
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130041429</v>
+        <v>130041603</v>
       </c>
       <c r="B12" t="n">
-        <v>79714</v>
+        <v>78761</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475441</v>
+        <v>475161</v>
       </c>
       <c r="R12" t="n">
-        <v>6832541</v>
+        <v>6832599</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130041518</v>
+        <v>130041429</v>
       </c>
       <c r="B13" t="n">
-        <v>91653</v>
+        <v>79714</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475537</v>
+        <v>475441</v>
       </c>
       <c r="R13" t="n">
-        <v>6832616</v>
+        <v>6832541</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,12 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På kulturved (gammal timmerstomme)</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130041603</v>
+        <v>130041518</v>
       </c>
       <c r="B14" t="n">
-        <v>78761</v>
+        <v>91653</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2009,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475161</v>
+        <v>475537</v>
       </c>
       <c r="R14" t="n">
-        <v>6832599</v>
+        <v>6832616</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2049,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På kulturved (gammal timmerstomme)</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2514,45 +2514,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130041483</v>
+        <v>130041476</v>
       </c>
       <c r="B19" t="n">
-        <v>79119</v>
+        <v>57741</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475269</v>
+        <v>475245</v>
       </c>
       <c r="R19" t="n">
-        <v>6832659</v>
+        <v>6832734</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2589,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2599,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,32 +2631,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130041597</v>
+        <v>130041483</v>
       </c>
       <c r="B20" t="n">
-        <v>79095</v>
+        <v>79119</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2656,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475391</v>
+        <v>475269</v>
       </c>
       <c r="R20" t="n">
-        <v>6832581</v>
+        <v>6832659</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2691,7 +2701,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2701,7 +2711,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,7 +2738,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130041543</v>
+        <v>130041597</v>
       </c>
       <c r="B21" t="n">
         <v>79095</v>
@@ -2763,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475124</v>
+        <v>475391</v>
       </c>
       <c r="R21" t="n">
-        <v>6832639</v>
+        <v>6832581</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2798,7 +2808,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2808,7 +2818,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,10 +2845,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130041442</v>
+        <v>130041543</v>
       </c>
       <c r="B22" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2846,21 +2856,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,10 +2880,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475303</v>
+        <v>475124</v>
       </c>
       <c r="R22" t="n">
-        <v>6832754</v>
+        <v>6832639</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,7 +2915,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2925,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130041476</v>
+        <v>130041442</v>
       </c>
       <c r="B23" t="n">
-        <v>57741</v>
+        <v>79714</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2953,39 +2963,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475245</v>
+        <v>475303</v>
       </c>
       <c r="R23" t="n">
-        <v>6832734</v>
+        <v>6832754</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,7 +3022,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3027,12 +3032,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4363,10 +4363,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130041524</v>
+        <v>130041430</v>
       </c>
       <c r="B36" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4374,21 +4374,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>475144</v>
+        <v>475161</v>
       </c>
       <c r="R36" t="n">
-        <v>6832586</v>
+        <v>6832599</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4470,10 +4470,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130041430</v>
+        <v>130041524</v>
       </c>
       <c r="B37" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>475161</v>
+        <v>475144</v>
       </c>
       <c r="R37" t="n">
-        <v>6832599</v>
+        <v>6832586</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5112,10 +5112,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130041475</v>
+        <v>130041575</v>
       </c>
       <c r="B43" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5123,39 +5123,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>475277</v>
+        <v>475266</v>
       </c>
       <c r="R43" t="n">
-        <v>6832740</v>
+        <v>6832803</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5187,7 +5182,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5197,12 +5192,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran), högst 5 år gamla</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5229,7 +5219,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130041575</v>
+        <v>130041588</v>
       </c>
       <c r="B44" t="n">
         <v>79095</v>
@@ -5264,10 +5254,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475266</v>
+        <v>475058</v>
       </c>
       <c r="R44" t="n">
-        <v>6832803</v>
+        <v>6832696</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5299,7 +5289,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5309,7 +5299,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5336,7 +5326,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130041588</v>
+        <v>130041571</v>
       </c>
       <c r="B45" t="n">
         <v>79095</v>
@@ -5371,10 +5361,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>475058</v>
+        <v>475307</v>
       </c>
       <c r="R45" t="n">
-        <v>6832696</v>
+        <v>6832773</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5406,7 +5396,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5416,7 +5406,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5443,7 +5433,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130041571</v>
+        <v>130041529</v>
       </c>
       <c r="B46" t="n">
         <v>79095</v>
@@ -5478,10 +5468,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475307</v>
+        <v>475095</v>
       </c>
       <c r="R46" t="n">
-        <v>6832773</v>
+        <v>6832582</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5513,7 +5503,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,7 +5513,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5550,7 +5540,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130041529</v>
+        <v>130041583</v>
       </c>
       <c r="B47" t="n">
         <v>79095</v>
@@ -5585,10 +5575,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>475095</v>
+        <v>475057</v>
       </c>
       <c r="R47" t="n">
-        <v>6832582</v>
+        <v>6832751</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5620,7 +5610,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5630,7 +5620,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5657,10 +5647,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130041583</v>
+        <v>130041475</v>
       </c>
       <c r="B48" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5668,34 +5658,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>475057</v>
+        <v>475277</v>
       </c>
       <c r="R48" t="n">
-        <v>6832751</v>
+        <v>6832740</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5727,7 +5722,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5737,7 +5732,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran), högst 5 år gamla</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5764,10 +5764,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130041449</v>
+        <v>130041570</v>
       </c>
       <c r="B49" t="n">
-        <v>79127</v>
+        <v>79095</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5775,21 +5775,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>475100</v>
+        <v>475287</v>
       </c>
       <c r="R49" t="n">
-        <v>6832696</v>
+        <v>6832747</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5871,32 +5871,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130041447</v>
+        <v>130041482</v>
       </c>
       <c r="B50" t="n">
-        <v>79127</v>
+        <v>79119</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6434</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>475447</v>
+        <v>475500</v>
       </c>
       <c r="R50" t="n">
-        <v>6832649</v>
+        <v>6832632</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5978,10 +5978,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130041450</v>
+        <v>130041565</v>
       </c>
       <c r="B51" t="n">
-        <v>79127</v>
+        <v>79095</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5989,21 +5989,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>475269</v>
+        <v>475456</v>
       </c>
       <c r="R51" t="n">
-        <v>6832659</v>
+        <v>6832651</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6085,7 +6085,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130041570</v>
+        <v>130041596</v>
       </c>
       <c r="B52" t="n">
         <v>79095</v>
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>475287</v>
+        <v>475378</v>
       </c>
       <c r="R52" t="n">
-        <v>6832747</v>
+        <v>6832576</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6192,32 +6192,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130041482</v>
+        <v>130041577</v>
       </c>
       <c r="B53" t="n">
-        <v>79119</v>
+        <v>79095</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>475500</v>
+        <v>475162</v>
       </c>
       <c r="R53" t="n">
-        <v>6832632</v>
+        <v>6832756</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6299,10 +6299,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130041565</v>
+        <v>130041449</v>
       </c>
       <c r="B54" t="n">
-        <v>79095</v>
+        <v>79127</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6310,21 +6310,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>475456</v>
+        <v>475100</v>
       </c>
       <c r="R54" t="n">
-        <v>6832651</v>
+        <v>6832696</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6406,10 +6406,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130041596</v>
+        <v>130041447</v>
       </c>
       <c r="B55" t="n">
-        <v>79095</v>
+        <v>79127</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6417,21 +6417,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>475378</v>
+        <v>475447</v>
       </c>
       <c r="R55" t="n">
-        <v>6832576</v>
+        <v>6832649</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6513,10 +6513,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130041577</v>
+        <v>130041450</v>
       </c>
       <c r="B56" t="n">
-        <v>79095</v>
+        <v>79127</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6524,21 +6524,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>475162</v>
+        <v>475269</v>
       </c>
       <c r="R56" t="n">
-        <v>6832756</v>
+        <v>6832659</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8245,7 +8245,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130041528</v>
+        <v>130041542</v>
       </c>
       <c r="B72" t="n">
         <v>79095</v>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>475072</v>
+        <v>475107</v>
       </c>
       <c r="R72" t="n">
-        <v>6832555</v>
+        <v>6832635</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8352,7 +8352,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130041589</v>
+        <v>130041528</v>
       </c>
       <c r="B73" t="n">
         <v>79095</v>
@@ -8387,10 +8387,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>475077</v>
+        <v>475072</v>
       </c>
       <c r="R73" t="n">
-        <v>6832687</v>
+        <v>6832555</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8459,7 +8459,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130041542</v>
+        <v>130041589</v>
       </c>
       <c r="B74" t="n">
         <v>79095</v>
@@ -8494,10 +8494,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>475107</v>
+        <v>475077</v>
       </c>
       <c r="R74" t="n">
-        <v>6832635</v>
+        <v>6832687</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8529,7 +8529,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 54495-2025 artfynd.xlsx
+++ b/artfynd/A 54495-2025 artfynd.xlsx
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130041595</v>
+        <v>130041603</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>78761</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475334</v>
+        <v>475161</v>
       </c>
       <c r="R9" t="n">
-        <v>6832589</v>
+        <v>6832599</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130041578</v>
+        <v>130041595</v>
       </c>
       <c r="B10" t="n">
         <v>79095</v>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475123</v>
+        <v>475334</v>
       </c>
       <c r="R10" t="n">
-        <v>6832763</v>
+        <v>6832589</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,7 +1648,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130041527</v>
+        <v>130041578</v>
       </c>
       <c r="B11" t="n">
         <v>79095</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475061</v>
+        <v>475123</v>
       </c>
       <c r="R11" t="n">
-        <v>6832499</v>
+        <v>6832763</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130041603</v>
+        <v>130041518</v>
       </c>
       <c r="B12" t="n">
-        <v>78761</v>
+        <v>91655</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475161</v>
+        <v>475537</v>
       </c>
       <c r="R12" t="n">
-        <v>6832599</v>
+        <v>6832616</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På kulturved (gammal timmerstomme)</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1969,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130041518</v>
+        <v>130041527</v>
       </c>
       <c r="B14" t="n">
-        <v>91653</v>
+        <v>79095</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,21 +1985,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475537</v>
+        <v>475061</v>
       </c>
       <c r="R14" t="n">
-        <v>6832616</v>
+        <v>6832499</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,12 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På kulturved (gammal timmerstomme)</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,45 +2081,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130041592</v>
+        <v>130041464</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>56931</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475196</v>
+        <v>475156</v>
       </c>
       <c r="R15" t="n">
-        <v>6832709</v>
+        <v>6832751</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,7 +2193,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130041593</v>
+        <v>130041592</v>
       </c>
       <c r="B16" t="n">
         <v>79095</v>
@@ -2223,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475269</v>
+        <v>475196</v>
       </c>
       <c r="R16" t="n">
-        <v>6832659</v>
+        <v>6832709</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,7 +2263,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2273,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,7 +2300,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130041522</v>
+        <v>130041593</v>
       </c>
       <c r="B17" t="n">
         <v>79095</v>
@@ -2330,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475323</v>
+        <v>475269</v>
       </c>
       <c r="R17" t="n">
-        <v>6832544</v>
+        <v>6832659</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,50 +2407,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130041464</v>
+        <v>130041522</v>
       </c>
       <c r="B18" t="n">
-        <v>56931</v>
+        <v>79095</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475156</v>
+        <v>475323</v>
       </c>
       <c r="R18" t="n">
-        <v>6832751</v>
+        <v>6832544</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2631,32 +2631,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130041483</v>
+        <v>130041442</v>
       </c>
       <c r="B20" t="n">
-        <v>79119</v>
+        <v>79714</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475269</v>
+        <v>475303</v>
       </c>
       <c r="R20" t="n">
-        <v>6832659</v>
+        <v>6832754</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2738,32 +2738,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130041597</v>
+        <v>130041483</v>
       </c>
       <c r="B21" t="n">
-        <v>79095</v>
+        <v>79119</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475391</v>
+        <v>475269</v>
       </c>
       <c r="R21" t="n">
-        <v>6832581</v>
+        <v>6832659</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,7 +2845,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130041543</v>
+        <v>130041597</v>
       </c>
       <c r="B22" t="n">
         <v>79095</v>
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475124</v>
+        <v>475391</v>
       </c>
       <c r="R22" t="n">
-        <v>6832639</v>
+        <v>6832581</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130041442</v>
+        <v>130041543</v>
       </c>
       <c r="B23" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,21 +2963,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475303</v>
+        <v>475124</v>
       </c>
       <c r="R23" t="n">
-        <v>6832754</v>
+        <v>6832639</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3818,10 +3818,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130041448</v>
+        <v>130041473</v>
       </c>
       <c r="B31" t="n">
-        <v>79127</v>
+        <v>57741</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3829,34 +3829,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>475341</v>
+        <v>475044</v>
       </c>
       <c r="R31" t="n">
-        <v>6832665</v>
+        <v>6832743</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3888,7 +3893,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3898,7 +3903,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3925,10 +3935,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130041473</v>
+        <v>130041448</v>
       </c>
       <c r="B32" t="n">
-        <v>57741</v>
+        <v>79127</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3936,39 +3946,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>475044</v>
+        <v>475341</v>
       </c>
       <c r="R32" t="n">
-        <v>6832743</v>
+        <v>6832665</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4000,7 +4005,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4010,12 +4015,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4149,7 +4149,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130041591</v>
+        <v>130041544</v>
       </c>
       <c r="B34" t="n">
         <v>79095</v>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>475155</v>
+        <v>475477</v>
       </c>
       <c r="R34" t="n">
-        <v>6832695</v>
+        <v>6832633</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4256,7 +4256,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130041544</v>
+        <v>130041591</v>
       </c>
       <c r="B35" t="n">
         <v>79095</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>475477</v>
+        <v>475155</v>
       </c>
       <c r="R35" t="n">
-        <v>6832633</v>
+        <v>6832695</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4791,7 +4791,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130041562</v>
+        <v>130041526</v>
       </c>
       <c r="B40" t="n">
         <v>79095</v>
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>475531</v>
+        <v>475142</v>
       </c>
       <c r="R40" t="n">
-        <v>6832619</v>
+        <v>6832509</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4898,7 +4898,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130041576</v>
+        <v>130041562</v>
       </c>
       <c r="B41" t="n">
         <v>79095</v>
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>475266</v>
+        <v>475531</v>
       </c>
       <c r="R41" t="n">
-        <v>6832776</v>
+        <v>6832619</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5005,7 +5005,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130041526</v>
+        <v>130041576</v>
       </c>
       <c r="B42" t="n">
         <v>79095</v>
@@ -5040,10 +5040,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>475142</v>
+        <v>475266</v>
       </c>
       <c r="R42" t="n">
-        <v>6832509</v>
+        <v>6832776</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6941,32 +6941,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130041500</v>
+        <v>130041443</v>
       </c>
       <c r="B60" t="n">
-        <v>57845</v>
+        <v>79127</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103031</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6976,10 +6976,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>475142</v>
+        <v>475509</v>
       </c>
       <c r="R60" t="n">
-        <v>6832509</v>
+        <v>6832511</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7048,10 +7048,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130041488</v>
+        <v>130041598</v>
       </c>
       <c r="B61" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7059,21 +7059,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>475161</v>
+        <v>475394</v>
       </c>
       <c r="R61" t="n">
-        <v>6832601</v>
+        <v>6832587</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7155,7 +7155,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130041598</v>
+        <v>130041566</v>
       </c>
       <c r="B62" t="n">
         <v>79095</v>
@@ -7190,10 +7190,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>475394</v>
+        <v>475443</v>
       </c>
       <c r="R62" t="n">
-        <v>6832587</v>
+        <v>6832633</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7225,7 +7225,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7262,45 +7262,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130041566</v>
+        <v>130041462</v>
       </c>
       <c r="B63" t="n">
-        <v>79095</v>
+        <v>56931</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>475443</v>
+        <v>475321</v>
       </c>
       <c r="R63" t="n">
-        <v>6832633</v>
+        <v>6832648</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7332,7 +7337,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7342,7 +7347,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Under betad tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7369,32 +7379,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130041443</v>
+        <v>130041500</v>
       </c>
       <c r="B64" t="n">
-        <v>79127</v>
+        <v>57845</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>103031</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7404,10 +7414,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>475509</v>
+        <v>475142</v>
       </c>
       <c r="R64" t="n">
-        <v>6832511</v>
+        <v>6832509</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7439,7 +7449,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7449,7 +7459,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7476,50 +7486,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130041462</v>
+        <v>130041488</v>
       </c>
       <c r="B65" t="n">
-        <v>56931</v>
+        <v>78853</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>475321</v>
+        <v>475161</v>
       </c>
       <c r="R65" t="n">
-        <v>6832648</v>
+        <v>6832601</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7551,7 +7556,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7561,12 +7566,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Under betad tall</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8245,10 +8245,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130041542</v>
+        <v>130041471</v>
       </c>
       <c r="B72" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8256,34 +8256,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>475107</v>
+        <v>475067</v>
       </c>
       <c r="R72" t="n">
-        <v>6832635</v>
+        <v>6832760</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8315,7 +8320,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8325,7 +8330,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8566,10 +8571,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130041471</v>
+        <v>130041542</v>
       </c>
       <c r="B75" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8577,39 +8582,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>475067</v>
+        <v>475107</v>
       </c>
       <c r="R75" t="n">
-        <v>6832760</v>
+        <v>6832635</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9004,37 +9004,42 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130044550</v>
+        <v>130044477</v>
       </c>
       <c r="B79" t="n">
-        <v>79095</v>
+        <v>56931</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9042,10 +9047,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>475214</v>
+        <v>475417</v>
       </c>
       <c r="R79" t="n">
-        <v>6832713</v>
+        <v>6832617</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9086,7 +9091,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9105,42 +9109,37 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130044477</v>
+        <v>130044550</v>
       </c>
       <c r="B80" t="n">
-        <v>56931</v>
+        <v>79095</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9148,10 +9147,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>475417</v>
+        <v>475214</v>
       </c>
       <c r="R80" t="n">
-        <v>6832617</v>
+        <v>6832713</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9192,6 +9191,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9518,10 +9518,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130044473</v>
+        <v>130044470</v>
       </c>
       <c r="B84" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9529,31 +9529,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9561,10 +9556,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>475417</v>
+        <v>475494</v>
       </c>
       <c r="R84" t="n">
-        <v>6832617</v>
+        <v>6832601</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9605,6 +9600,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9623,10 +9619,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130044470</v>
+        <v>130044473</v>
       </c>
       <c r="B85" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9634,26 +9630,31 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -9661,10 +9662,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>475494</v>
+        <v>475417</v>
       </c>
       <c r="R85" t="n">
-        <v>6832601</v>
+        <v>6832617</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9705,7 +9706,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9930,10 +9930,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130044486</v>
+        <v>130044552</v>
       </c>
       <c r="B88" t="n">
-        <v>91639</v>
+        <v>79714</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9941,21 +9941,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9968,10 +9968,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>475308</v>
+        <v>475214</v>
       </c>
       <c r="R88" t="n">
-        <v>6832714</v>
+        <v>6832713</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10031,10 +10031,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130044552</v>
+        <v>130044486</v>
       </c>
       <c r="B89" t="n">
-        <v>79714</v>
+        <v>91641</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10042,21 +10042,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10069,10 +10069,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>475214</v>
+        <v>475308</v>
       </c>
       <c r="R89" t="n">
-        <v>6832713</v>
+        <v>6832714</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 54495-2025 artfynd.xlsx
+++ b/artfynd/A 54495-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130041585</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130041599</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130041525</v>
+        <v>130041582</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475108</v>
+        <v>475060</v>
       </c>
       <c r="R4" t="n">
-        <v>6832521</v>
+        <v>6832756</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130041582</v>
+        <v>130041525</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475060</v>
+        <v>475108</v>
       </c>
       <c r="R5" t="n">
-        <v>6832756</v>
+        <v>6832521</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130041579</v>
+        <v>130041478</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475095</v>
+        <v>475186</v>
       </c>
       <c r="R6" t="n">
-        <v>6832782</v>
+        <v>6832701</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1188,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130041478</v>
+        <v>130041579</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,39 +1231,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475186</v>
+        <v>475095</v>
       </c>
       <c r="R7" t="n">
-        <v>6832701</v>
+        <v>6832782</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,12 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,7 +1330,7 @@
         <v>130041502</v>
       </c>
       <c r="B8" t="n">
-        <v>81080</v>
+        <v>81165</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130041603</v>
+        <v>130041429</v>
       </c>
       <c r="B9" t="n">
-        <v>78761</v>
+        <v>79799</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475161</v>
+        <v>475441</v>
       </c>
       <c r="R9" t="n">
-        <v>6832599</v>
+        <v>6832541</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,7 +1544,7 @@
         <v>130041595</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>130041578</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>130041518</v>
       </c>
       <c r="B12" t="n">
-        <v>91655</v>
+        <v>91742</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130041429</v>
+        <v>130041603</v>
       </c>
       <c r="B13" t="n">
-        <v>79714</v>
+        <v>78846</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,21 +1878,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475441</v>
+        <v>475161</v>
       </c>
       <c r="R13" t="n">
-        <v>6832541</v>
+        <v>6832599</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,7 +1977,7 @@
         <v>130041527</v>
       </c>
       <c r="B14" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,50 +2081,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130041464</v>
+        <v>130041592</v>
       </c>
       <c r="B15" t="n">
-        <v>56931</v>
+        <v>79180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475156</v>
+        <v>475196</v>
       </c>
       <c r="R15" t="n">
-        <v>6832751</v>
+        <v>6832709</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130041592</v>
+        <v>130041593</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475196</v>
+        <v>475269</v>
       </c>
       <c r="R16" t="n">
-        <v>6832709</v>
+        <v>6832659</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130041593</v>
+        <v>130041522</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475269</v>
+        <v>475323</v>
       </c>
       <c r="R17" t="n">
-        <v>6832659</v>
+        <v>6832544</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,45 +2402,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130041522</v>
+        <v>130041464</v>
       </c>
       <c r="B18" t="n">
-        <v>79095</v>
+        <v>57016</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475323</v>
+        <v>475156</v>
       </c>
       <c r="R18" t="n">
-        <v>6832544</v>
+        <v>6832751</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,50 +2514,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130041476</v>
+        <v>130041483</v>
       </c>
       <c r="B19" t="n">
-        <v>57741</v>
+        <v>79204</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475245</v>
+        <v>475269</v>
       </c>
       <c r="R19" t="n">
-        <v>6832734</v>
+        <v>6832659</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2599,12 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2631,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130041442</v>
+        <v>130041476</v>
       </c>
       <c r="B20" t="n">
-        <v>79714</v>
+        <v>57826</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,34 +2632,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475303</v>
+        <v>475245</v>
       </c>
       <c r="R20" t="n">
-        <v>6832754</v>
+        <v>6832734</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2701,7 +2696,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2711,7 +2706,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2738,32 +2738,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130041483</v>
+        <v>130041442</v>
       </c>
       <c r="B21" t="n">
-        <v>79119</v>
+        <v>79799</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475269</v>
+        <v>475303</v>
       </c>
       <c r="R21" t="n">
-        <v>6832659</v>
+        <v>6832754</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2848,7 +2848,7 @@
         <v>130041597</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,45 +2952,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130041543</v>
+        <v>130041465</v>
       </c>
       <c r="B23" t="n">
-        <v>79095</v>
+        <v>57016</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475124</v>
+        <v>475430</v>
       </c>
       <c r="R23" t="n">
-        <v>6832639</v>
+        <v>6832587</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3022,7 +3027,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3032,7 +3037,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,50 +3064,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130041465</v>
+        <v>130041543</v>
       </c>
       <c r="B24" t="n">
-        <v>56931</v>
+        <v>79180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475430</v>
+        <v>475124</v>
       </c>
       <c r="R24" t="n">
-        <v>6832587</v>
+        <v>6832639</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3174,7 +3174,7 @@
         <v>130041590</v>
       </c>
       <c r="B25" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>130041572</v>
       </c>
       <c r="B26" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130041608</v>
+        <v>130041461</v>
       </c>
       <c r="B27" t="n">
-        <v>78498</v>
+        <v>57826</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,34 +3396,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>475113</v>
+        <v>475283</v>
       </c>
       <c r="R27" t="n">
-        <v>6832544</v>
+        <v>6832744</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3455,7 +3460,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3465,7 +3470,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3492,10 +3497,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130041461</v>
+        <v>130041608</v>
       </c>
       <c r="B28" t="n">
-        <v>57741</v>
+        <v>78583</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3503,39 +3508,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>475283</v>
+        <v>475113</v>
       </c>
       <c r="R28" t="n">
-        <v>6832744</v>
+        <v>6832544</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3604,10 +3604,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130041573</v>
+        <v>130041448</v>
       </c>
       <c r="B29" t="n">
-        <v>79095</v>
+        <v>79212</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3615,21 +3615,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>475283</v>
+        <v>475341</v>
       </c>
       <c r="R29" t="n">
-        <v>6832815</v>
+        <v>6832665</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3711,10 +3711,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130041584</v>
+        <v>130041473</v>
       </c>
       <c r="B30" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3722,34 +3722,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>475036</v>
+        <v>475044</v>
       </c>
       <c r="R30" t="n">
-        <v>6832748</v>
+        <v>6832743</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3781,7 +3786,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3791,7 +3796,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3818,10 +3828,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130041473</v>
+        <v>130041573</v>
       </c>
       <c r="B31" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3829,39 +3839,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>475044</v>
+        <v>475283</v>
       </c>
       <c r="R31" t="n">
-        <v>6832743</v>
+        <v>6832815</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3893,7 +3898,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3903,12 +3908,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3935,10 +3935,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130041448</v>
+        <v>130041584</v>
       </c>
       <c r="B32" t="n">
-        <v>79127</v>
+        <v>79180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3946,21 +3946,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>475341</v>
+        <v>475036</v>
       </c>
       <c r="R32" t="n">
-        <v>6832665</v>
+        <v>6832748</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4045,7 +4045,7 @@
         <v>130041602</v>
       </c>
       <c r="B33" t="n">
-        <v>78761</v>
+        <v>78846</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130041544</v>
+        <v>130041591</v>
       </c>
       <c r="B34" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>475477</v>
+        <v>475155</v>
       </c>
       <c r="R34" t="n">
-        <v>6832633</v>
+        <v>6832695</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4256,10 +4256,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130041591</v>
+        <v>130041544</v>
       </c>
       <c r="B35" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>475155</v>
+        <v>475477</v>
       </c>
       <c r="R35" t="n">
-        <v>6832695</v>
+        <v>6832633</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4366,7 +4366,7 @@
         <v>130041430</v>
       </c>
       <c r="B36" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>130041524</v>
       </c>
       <c r="B37" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>130041594</v>
       </c>
       <c r="B38" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>130041600</v>
       </c>
       <c r="B39" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4791,10 +4791,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130041526</v>
+        <v>130041562</v>
       </c>
       <c r="B40" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>475142</v>
+        <v>475531</v>
       </c>
       <c r="R40" t="n">
-        <v>6832509</v>
+        <v>6832619</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4898,10 +4898,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130041562</v>
+        <v>130041576</v>
       </c>
       <c r="B41" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>475531</v>
+        <v>475266</v>
       </c>
       <c r="R41" t="n">
-        <v>6832619</v>
+        <v>6832776</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5005,10 +5005,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130041576</v>
+        <v>130041526</v>
       </c>
       <c r="B42" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5040,10 +5040,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>475266</v>
+        <v>475142</v>
       </c>
       <c r="R42" t="n">
-        <v>6832776</v>
+        <v>6832509</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5112,10 +5112,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130041575</v>
+        <v>130041571</v>
       </c>
       <c r="B43" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>475266</v>
+        <v>475307</v>
       </c>
       <c r="R43" t="n">
-        <v>6832803</v>
+        <v>6832773</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5182,7 +5182,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5219,10 +5219,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130041588</v>
+        <v>130041575</v>
       </c>
       <c r="B44" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5254,10 +5254,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475058</v>
+        <v>475266</v>
       </c>
       <c r="R44" t="n">
-        <v>6832696</v>
+        <v>6832803</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5326,10 +5326,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130041571</v>
+        <v>130041588</v>
       </c>
       <c r="B45" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>475307</v>
+        <v>475058</v>
       </c>
       <c r="R45" t="n">
-        <v>6832773</v>
+        <v>6832696</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5436,7 +5436,7 @@
         <v>130041529</v>
       </c>
       <c r="B46" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5540,10 +5540,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130041583</v>
+        <v>130041475</v>
       </c>
       <c r="B47" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5551,34 +5551,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>475057</v>
+        <v>475277</v>
       </c>
       <c r="R47" t="n">
-        <v>6832751</v>
+        <v>6832740</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5610,7 +5615,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5620,7 +5625,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran), högst 5 år gamla</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5647,10 +5657,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130041475</v>
+        <v>130041583</v>
       </c>
       <c r="B48" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5658,39 +5668,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>475277</v>
+        <v>475057</v>
       </c>
       <c r="R48" t="n">
-        <v>6832740</v>
+        <v>6832751</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5722,7 +5727,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5732,12 +5737,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran), högst 5 år gamla</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5764,10 +5764,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130041570</v>
+        <v>130041449</v>
       </c>
       <c r="B49" t="n">
-        <v>79095</v>
+        <v>79212</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5775,21 +5775,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>475287</v>
+        <v>475100</v>
       </c>
       <c r="R49" t="n">
-        <v>6832747</v>
+        <v>6832696</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5871,32 +5871,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130041482</v>
+        <v>130041447</v>
       </c>
       <c r="B50" t="n">
-        <v>79119</v>
+        <v>79212</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6434</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>475500</v>
+        <v>475447</v>
       </c>
       <c r="R50" t="n">
-        <v>6832632</v>
+        <v>6832649</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5978,10 +5978,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130041565</v>
+        <v>130041570</v>
       </c>
       <c r="B51" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>475456</v>
+        <v>475287</v>
       </c>
       <c r="R51" t="n">
-        <v>6832651</v>
+        <v>6832747</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6085,10 +6085,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130041596</v>
+        <v>130041450</v>
       </c>
       <c r="B52" t="n">
-        <v>79095</v>
+        <v>79212</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6096,21 +6096,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>475378</v>
+        <v>475269</v>
       </c>
       <c r="R52" t="n">
-        <v>6832576</v>
+        <v>6832659</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6192,10 +6192,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130041577</v>
+        <v>130041458</v>
       </c>
       <c r="B53" t="n">
-        <v>79095</v>
+        <v>79770</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6203,21 +6203,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>475162</v>
+        <v>475113</v>
       </c>
       <c r="R53" t="n">
-        <v>6832756</v>
+        <v>6832543</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6299,32 +6299,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130041449</v>
+        <v>130041482</v>
       </c>
       <c r="B54" t="n">
-        <v>79127</v>
+        <v>79204</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>6434</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>475100</v>
+        <v>475500</v>
       </c>
       <c r="R54" t="n">
-        <v>6832696</v>
+        <v>6832632</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6406,10 +6406,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130041447</v>
+        <v>130041565</v>
       </c>
       <c r="B55" t="n">
-        <v>79127</v>
+        <v>79180</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6417,21 +6417,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>475447</v>
+        <v>475456</v>
       </c>
       <c r="R55" t="n">
-        <v>6832649</v>
+        <v>6832651</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6513,10 +6513,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130041450</v>
+        <v>130041596</v>
       </c>
       <c r="B56" t="n">
-        <v>79127</v>
+        <v>79180</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6524,21 +6524,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>475269</v>
+        <v>475378</v>
       </c>
       <c r="R56" t="n">
-        <v>6832659</v>
+        <v>6832576</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6620,10 +6620,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130041458</v>
+        <v>130041577</v>
       </c>
       <c r="B57" t="n">
-        <v>79685</v>
+        <v>79180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6631,21 +6631,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>475113</v>
+        <v>475162</v>
       </c>
       <c r="R57" t="n">
-        <v>6832543</v>
+        <v>6832756</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6730,7 +6730,7 @@
         <v>130041498</v>
       </c>
       <c r="B58" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>130041574</v>
       </c>
       <c r="B59" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>130041443</v>
       </c>
       <c r="B60" t="n">
-        <v>79127</v>
+        <v>79212</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7048,32 +7048,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130041598</v>
+        <v>130041500</v>
       </c>
       <c r="B61" t="n">
-        <v>79095</v>
+        <v>57930</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>475394</v>
+        <v>475142</v>
       </c>
       <c r="R61" t="n">
-        <v>6832587</v>
+        <v>6832509</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7155,10 +7155,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130041566</v>
+        <v>130041598</v>
       </c>
       <c r="B62" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7190,10 +7190,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>475443</v>
+        <v>475394</v>
       </c>
       <c r="R62" t="n">
-        <v>6832633</v>
+        <v>6832587</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7225,7 +7225,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7262,50 +7262,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130041462</v>
+        <v>130041488</v>
       </c>
       <c r="B63" t="n">
-        <v>56931</v>
+        <v>78938</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>475321</v>
+        <v>475161</v>
       </c>
       <c r="R63" t="n">
-        <v>6832648</v>
+        <v>6832601</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7337,7 +7332,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7347,12 +7342,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Under betad tall</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7379,32 +7369,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130041500</v>
+        <v>130041566</v>
       </c>
       <c r="B64" t="n">
-        <v>57845</v>
+        <v>79180</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7414,10 +7404,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>475142</v>
+        <v>475443</v>
       </c>
       <c r="R64" t="n">
-        <v>6832509</v>
+        <v>6832633</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7449,7 +7439,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7459,7 +7449,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7486,45 +7476,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130041488</v>
+        <v>130041462</v>
       </c>
       <c r="B65" t="n">
-        <v>78853</v>
+        <v>57016</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>475161</v>
+        <v>475321</v>
       </c>
       <c r="R65" t="n">
-        <v>6832601</v>
+        <v>6832648</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7556,7 +7551,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7566,7 +7561,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Under betad tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7596,7 +7596,7 @@
         <v>130041586</v>
       </c>
       <c r="B66" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7700,45 +7700,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130041568</v>
+        <v>130041463</v>
       </c>
       <c r="B67" t="n">
-        <v>79095</v>
+        <v>57016</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>475381</v>
+        <v>475317</v>
       </c>
       <c r="R67" t="n">
-        <v>6832661</v>
+        <v>6832770</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7770,7 +7775,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7780,7 +7785,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Under betad tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7807,10 +7817,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130041567</v>
+        <v>130041568</v>
       </c>
       <c r="B68" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7842,10 +7852,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>475450</v>
+        <v>475381</v>
       </c>
       <c r="R68" t="n">
-        <v>6832632</v>
+        <v>6832661</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7877,7 +7887,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7887,7 +7897,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7914,10 +7924,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130041563</v>
+        <v>130041567</v>
       </c>
       <c r="B69" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7949,10 +7959,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>475527</v>
+        <v>475450</v>
       </c>
       <c r="R69" t="n">
-        <v>6832623</v>
+        <v>6832632</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7984,7 +7994,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7994,7 +8004,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8021,10 +8031,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130041564</v>
+        <v>130041563</v>
       </c>
       <c r="B70" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8056,10 +8066,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>475461</v>
+        <v>475527</v>
       </c>
       <c r="R70" t="n">
-        <v>6832659</v>
+        <v>6832623</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8091,7 +8101,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8101,7 +8111,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8128,50 +8138,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130041463</v>
+        <v>130041564</v>
       </c>
       <c r="B71" t="n">
-        <v>56931</v>
+        <v>79180</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>475317</v>
+        <v>475461</v>
       </c>
       <c r="R71" t="n">
-        <v>6832770</v>
+        <v>6832659</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8203,7 +8208,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8213,12 +8218,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Under betad tall</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8245,38 +8245,38 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130041471</v>
+        <v>130041466</v>
       </c>
       <c r="B72" t="n">
-        <v>57738</v>
+        <v>57016</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>475067</v>
+        <v>475445</v>
       </c>
       <c r="R72" t="n">
-        <v>6832760</v>
+        <v>6832605</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8360,7 +8360,7 @@
         <v>130041528</v>
       </c>
       <c r="B73" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>130041589</v>
       </c>
       <c r="B74" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>130041542</v>
       </c>
       <c r="B75" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8678,38 +8678,38 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130041466</v>
+        <v>130041471</v>
       </c>
       <c r="B76" t="n">
-        <v>56931</v>
+        <v>57823</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8718,10 +8718,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>475445</v>
+        <v>475067</v>
       </c>
       <c r="R76" t="n">
-        <v>6832605</v>
+        <v>6832760</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8793,7 +8793,7 @@
         <v>130041523</v>
       </c>
       <c r="B77" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>130041580</v>
       </c>
       <c r="B78" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>130044477</v>
       </c>
       <c r="B79" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>130044550</v>
       </c>
       <c r="B80" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>130044472</v>
       </c>
       <c r="B81" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>130044543</v>
       </c>
       <c r="B82" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>130044494</v>
       </c>
       <c r="B83" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>130044470</v>
       </c>
       <c r="B84" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>130044473</v>
       </c>
       <c r="B85" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>130044482</v>
       </c>
       <c r="B86" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>130044484</v>
       </c>
       <c r="B87" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9930,10 +9930,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130044552</v>
+        <v>130044486</v>
       </c>
       <c r="B88" t="n">
-        <v>79714</v>
+        <v>91728</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9941,21 +9941,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9968,10 +9968,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>475214</v>
+        <v>475308</v>
       </c>
       <c r="R88" t="n">
-        <v>6832713</v>
+        <v>6832714</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10031,10 +10031,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130044486</v>
+        <v>130044552</v>
       </c>
       <c r="B89" t="n">
-        <v>91641</v>
+        <v>79799</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10042,21 +10042,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10069,10 +10069,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>475308</v>
+        <v>475214</v>
       </c>
       <c r="R89" t="n">
-        <v>6832714</v>
+        <v>6832713</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10135,7 +10135,7 @@
         <v>130044501</v>
       </c>
       <c r="B90" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10233,10 +10233,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130044571</v>
+        <v>130044481</v>
       </c>
       <c r="B91" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10244,26 +10244,31 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10271,10 +10276,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>475209</v>
+        <v>475386</v>
       </c>
       <c r="R91" t="n">
-        <v>6832640</v>
+        <v>6832591</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10315,7 +10320,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10334,10 +10338,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130044481</v>
+        <v>130044571</v>
       </c>
       <c r="B92" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10345,31 +10349,26 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -10377,10 +10376,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>475386</v>
+        <v>475209</v>
       </c>
       <c r="R92" t="n">
-        <v>6832591</v>
+        <v>6832640</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10421,6 +10420,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10442,7 +10442,7 @@
         <v>130044565</v>
       </c>
       <c r="B93" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>130044480</v>
       </c>
       <c r="B94" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>130060248</v>
       </c>
       <c r="B95" t="n">
-        <v>78498</v>
+        <v>78583</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 54495-2025 artfynd.xlsx
+++ b/artfynd/A 54495-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AY100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130041585</v>
+        <v>130041443</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475050</v>
+        <v>475509</v>
       </c>
       <c r="R2" t="n">
-        <v>6832721</v>
+        <v>6832511</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130041599</v>
+        <v>130041447</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475445</v>
+        <v>475447</v>
       </c>
       <c r="R3" t="n">
-        <v>6832596</v>
+        <v>6832649</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130041502</v>
+        <v>130041448</v>
       </c>
       <c r="B4" t="n">
-        <v>81165</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475113</v>
+        <v>475341</v>
       </c>
       <c r="R4" t="n">
-        <v>6832544</v>
+        <v>6832665</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130041478</v>
+        <v>130041449</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475186</v>
+        <v>475100</v>
       </c>
       <c r="R5" t="n">
-        <v>6832701</v>
+        <v>6832696</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130041525</v>
+        <v>130041450</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475108</v>
+        <v>475269</v>
       </c>
       <c r="R6" t="n">
-        <v>6832521</v>
+        <v>6832659</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130041582</v>
+        <v>130041602</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475060</v>
+        <v>475161</v>
       </c>
       <c r="R7" t="n">
-        <v>6832756</v>
+        <v>6832601</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130041579</v>
+        <v>130041603</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475095</v>
+        <v>475161</v>
       </c>
       <c r="R8" t="n">
-        <v>6832782</v>
+        <v>6832599</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130041595</v>
+        <v>130041502</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>81312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475334</v>
+        <v>475113</v>
       </c>
       <c r="R9" t="n">
-        <v>6832589</v>
+        <v>6832544</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130041578</v>
+        <v>130044486</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,34 +1542,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475123</v>
+        <v>475308</v>
       </c>
       <c r="R10" t="n">
-        <v>6832763</v>
+        <v>6832714</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,71 +1602,62 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130041429</v>
+        <v>130041518</v>
       </c>
       <c r="B11" t="n">
-        <v>79799</v>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475441</v>
+        <v>475537</v>
       </c>
       <c r="R11" t="n">
-        <v>6832541</v>
+        <v>6832616</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1702,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1712,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På kulturved (gammal timmerstomme)</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,14 +1744,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130041527</v>
+        <v>130041522</v>
       </c>
       <c r="B12" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1790,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475061</v>
+        <v>475323</v>
       </c>
       <c r="R12" t="n">
-        <v>6832499</v>
+        <v>6832544</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1814,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1824,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,32 +1851,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130041603</v>
+        <v>130041523</v>
       </c>
       <c r="B13" t="n">
-        <v>78846</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475161</v>
+        <v>475171</v>
       </c>
       <c r="R13" t="n">
-        <v>6832599</v>
+        <v>6832605</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1921,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1931,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,32 +1958,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130041518</v>
+        <v>130041524</v>
       </c>
       <c r="B14" t="n">
-        <v>91742</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,10 +1993,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475537</v>
+        <v>475144</v>
       </c>
       <c r="R14" t="n">
-        <v>6832616</v>
+        <v>6832586</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2028,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,12 +2038,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På kulturved (gammal timmerstomme)</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,14 +2065,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130041593</v>
+        <v>130041525</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2116,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475269</v>
+        <v>475108</v>
       </c>
       <c r="R15" t="n">
-        <v>6832659</v>
+        <v>6832521</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2135,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2145,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,50 +2172,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130041464</v>
+        <v>130041526</v>
       </c>
       <c r="B16" t="n">
-        <v>57016</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475156</v>
+        <v>475142</v>
       </c>
       <c r="R16" t="n">
-        <v>6832751</v>
+        <v>6832509</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2242,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2252,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,14 +2279,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130041592</v>
+        <v>130041527</v>
       </c>
       <c r="B17" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2335,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475196</v>
+        <v>475061</v>
       </c>
       <c r="R17" t="n">
-        <v>6832709</v>
+        <v>6832499</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2349,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2359,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,14 +2386,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130041522</v>
+        <v>130041528</v>
       </c>
       <c r="B18" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2442,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475323</v>
+        <v>475072</v>
       </c>
       <c r="R18" t="n">
-        <v>6832544</v>
+        <v>6832555</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2456,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2466,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,32 +2493,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130041442</v>
+        <v>130041529</v>
       </c>
       <c r="B19" t="n">
-        <v>79799</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,10 +2528,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475303</v>
+        <v>475095</v>
       </c>
       <c r="R19" t="n">
-        <v>6832754</v>
+        <v>6832582</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2563,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2573,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,32 +2600,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130041483</v>
+        <v>130041530</v>
       </c>
       <c r="B20" t="n">
-        <v>79204</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2656,10 +2635,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475269</v>
+        <v>475046</v>
       </c>
       <c r="R20" t="n">
-        <v>6832659</v>
+        <v>6832577</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2691,7 +2670,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2701,7 +2680,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,14 +2707,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130041597</v>
+        <v>130041531</v>
       </c>
       <c r="B21" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2763,10 +2742,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475391</v>
+        <v>475043</v>
       </c>
       <c r="R21" t="n">
-        <v>6832581</v>
+        <v>6832554</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2798,7 +2777,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2808,7 +2787,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,50 +2814,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130041476</v>
+        <v>130041532</v>
       </c>
       <c r="B22" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475245</v>
+        <v>475034</v>
       </c>
       <c r="R22" t="n">
-        <v>6832734</v>
+        <v>6832550</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,7 +2884,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2920,12 +2894,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,50 +2921,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130041465</v>
+        <v>130041540</v>
       </c>
       <c r="B23" t="n">
-        <v>57016</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475430</v>
+        <v>475031</v>
       </c>
       <c r="R23" t="n">
-        <v>6832587</v>
+        <v>6832665</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3027,7 +2991,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3037,7 +3001,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3064,14 +3028,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130041543</v>
+        <v>130041542</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3099,10 +3063,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475124</v>
+        <v>475107</v>
       </c>
       <c r="R24" t="n">
-        <v>6832639</v>
+        <v>6832635</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3134,7 +3098,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3144,7 +3108,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3171,50 +3135,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130041461</v>
+        <v>130041543</v>
       </c>
       <c r="B25" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475283</v>
+        <v>475124</v>
       </c>
       <c r="R25" t="n">
-        <v>6832744</v>
+        <v>6832639</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3246,7 +3205,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3256,14 +3215,14 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="b">
         <v>0</v>
@@ -3283,14 +3242,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130041590</v>
+        <v>130041544</v>
       </c>
       <c r="B26" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3318,10 +3277,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475119</v>
+        <v>475477</v>
       </c>
       <c r="R26" t="n">
-        <v>6832699</v>
+        <v>6832633</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3353,7 +3312,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3363,7 +3322,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3390,14 +3349,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130041572</v>
+        <v>130041562</v>
       </c>
       <c r="B27" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3425,10 +3384,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>475301</v>
+        <v>475531</v>
       </c>
       <c r="R27" t="n">
-        <v>6832783</v>
+        <v>6832619</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3460,7 +3419,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3470,7 +3429,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3497,32 +3456,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130041608</v>
+        <v>130041563</v>
       </c>
       <c r="B28" t="n">
-        <v>78583</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3532,10 +3491,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>475113</v>
+        <v>475527</v>
       </c>
       <c r="R28" t="n">
-        <v>6832544</v>
+        <v>6832623</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3567,7 +3526,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3577,7 +3536,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3604,14 +3563,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130041573</v>
+        <v>130041564</v>
       </c>
       <c r="B29" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3639,10 +3598,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>475283</v>
+        <v>475461</v>
       </c>
       <c r="R29" t="n">
-        <v>6832815</v>
+        <v>6832659</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3674,7 +3633,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3684,7 +3643,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3711,14 +3670,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130041584</v>
+        <v>130041565</v>
       </c>
       <c r="B30" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3746,10 +3705,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>475036</v>
+        <v>475456</v>
       </c>
       <c r="R30" t="n">
-        <v>6832748</v>
+        <v>6832651</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3781,7 +3740,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3791,7 +3750,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3818,32 +3777,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130041448</v>
+        <v>130041566</v>
       </c>
       <c r="B31" t="n">
-        <v>79212</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3853,10 +3812,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>475341</v>
+        <v>475443</v>
       </c>
       <c r="R31" t="n">
-        <v>6832665</v>
+        <v>6832633</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3888,7 +3847,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3898,7 +3857,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3925,50 +3884,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130041473</v>
+        <v>130041567</v>
       </c>
       <c r="B32" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>475044</v>
+        <v>475450</v>
       </c>
       <c r="R32" t="n">
-        <v>6832743</v>
+        <v>6832632</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4000,7 +3954,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4010,12 +3964,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4042,32 +3991,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130041602</v>
+        <v>130041568</v>
       </c>
       <c r="B33" t="n">
-        <v>78846</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4077,10 +4026,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>475161</v>
+        <v>475381</v>
       </c>
       <c r="R33" t="n">
-        <v>6832601</v>
+        <v>6832661</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4112,7 +4061,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4122,7 +4071,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4149,14 +4098,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130041591</v>
+        <v>130041569</v>
       </c>
       <c r="B34" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4184,10 +4133,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>475155</v>
+        <v>475381</v>
       </c>
       <c r="R34" t="n">
-        <v>6832695</v>
+        <v>6832670</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4219,7 +4168,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4229,7 +4178,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4256,14 +4205,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130041544</v>
+        <v>130041570</v>
       </c>
       <c r="B35" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4291,10 +4240,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>475477</v>
+        <v>475287</v>
       </c>
       <c r="R35" t="n">
-        <v>6832633</v>
+        <v>6832747</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4326,7 +4275,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4336,7 +4285,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4363,14 +4312,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130041524</v>
+        <v>130041571</v>
       </c>
       <c r="B36" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4398,10 +4347,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>475144</v>
+        <v>475307</v>
       </c>
       <c r="R36" t="n">
-        <v>6832586</v>
+        <v>6832773</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4433,7 +4382,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4443,7 +4392,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4470,32 +4419,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130041430</v>
+        <v>130041572</v>
       </c>
       <c r="B37" t="n">
-        <v>79799</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4505,10 +4454,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>475161</v>
+        <v>475301</v>
       </c>
       <c r="R37" t="n">
-        <v>6832599</v>
+        <v>6832783</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4540,7 +4489,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4550,7 +4499,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4577,14 +4526,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130041594</v>
+        <v>130041573</v>
       </c>
       <c r="B38" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4612,10 +4561,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>475287</v>
+        <v>475283</v>
       </c>
       <c r="R38" t="n">
-        <v>6832631</v>
+        <v>6832815</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4647,7 +4596,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4657,7 +4606,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4684,14 +4633,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130041600</v>
+        <v>130041574</v>
       </c>
       <c r="B39" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4719,10 +4668,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>475471</v>
+        <v>475268</v>
       </c>
       <c r="R39" t="n">
-        <v>6832571</v>
+        <v>6832805</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4754,7 +4703,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4764,7 +4713,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4791,14 +4740,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130041562</v>
+        <v>130041575</v>
       </c>
       <c r="B40" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4826,10 +4775,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>475531</v>
+        <v>475266</v>
       </c>
       <c r="R40" t="n">
-        <v>6832619</v>
+        <v>6832803</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4861,7 +4810,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4871,7 +4820,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4901,11 +4850,11 @@
         <v>130041576</v>
       </c>
       <c r="B41" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -5005,14 +4954,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130041526</v>
+        <v>130041577</v>
       </c>
       <c r="B42" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5040,10 +4989,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>475142</v>
+        <v>475162</v>
       </c>
       <c r="R42" t="n">
-        <v>6832509</v>
+        <v>6832756</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5075,7 +5024,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5085,7 +5034,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5112,50 +5061,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130041475</v>
+        <v>130041578</v>
       </c>
       <c r="B43" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>475277</v>
+        <v>475123</v>
       </c>
       <c r="R43" t="n">
-        <v>6832740</v>
+        <v>6832763</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5187,7 +5131,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5197,12 +5141,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran), högst 5 år gamla</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5229,14 +5168,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130041588</v>
+        <v>130041579</v>
       </c>
       <c r="B44" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5264,10 +5203,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475058</v>
+        <v>475095</v>
       </c>
       <c r="R44" t="n">
-        <v>6832696</v>
+        <v>6832782</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5299,7 +5238,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5309,7 +5248,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5336,14 +5275,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130041571</v>
+        <v>130041580</v>
       </c>
       <c r="B45" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5371,10 +5310,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>475307</v>
+        <v>475066</v>
       </c>
       <c r="R45" t="n">
-        <v>6832773</v>
+        <v>6832769</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5406,7 +5345,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5416,7 +5355,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5443,14 +5382,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130041583</v>
+        <v>130041582</v>
       </c>
       <c r="B46" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5478,10 +5417,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475057</v>
+        <v>475060</v>
       </c>
       <c r="R46" t="n">
-        <v>6832751</v>
+        <v>6832756</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5550,14 +5489,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130041575</v>
+        <v>130041583</v>
       </c>
       <c r="B47" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5585,10 +5524,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>475266</v>
+        <v>475057</v>
       </c>
       <c r="R47" t="n">
-        <v>6832803</v>
+        <v>6832751</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5620,7 +5559,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5630,7 +5569,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5657,14 +5596,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130041529</v>
+        <v>130041584</v>
       </c>
       <c r="B48" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5692,10 +5631,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>475095</v>
+        <v>475036</v>
       </c>
       <c r="R48" t="n">
-        <v>6832582</v>
+        <v>6832748</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5727,7 +5666,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5737,7 +5676,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5764,32 +5703,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130041450</v>
+        <v>130041585</v>
       </c>
       <c r="B49" t="n">
-        <v>79212</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5799,10 +5738,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>475269</v>
+        <v>475050</v>
       </c>
       <c r="R49" t="n">
-        <v>6832659</v>
+        <v>6832721</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5834,7 +5773,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5844,7 +5783,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5871,32 +5810,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130041447</v>
+        <v>130041586</v>
       </c>
       <c r="B50" t="n">
-        <v>79212</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5906,10 +5845,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>475447</v>
+        <v>475055</v>
       </c>
       <c r="R50" t="n">
-        <v>6832649</v>
+        <v>6832711</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5941,7 +5880,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5951,7 +5890,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5978,32 +5917,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130041449</v>
+        <v>130041588</v>
       </c>
       <c r="B51" t="n">
-        <v>79212</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6013,7 +5952,7 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>475100</v>
+        <v>475058</v>
       </c>
       <c r="R51" t="n">
         <v>6832696</v>
@@ -6048,7 +5987,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6058,7 +5997,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6085,14 +6024,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130041570</v>
+        <v>130041589</v>
       </c>
       <c r="B52" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -6120,10 +6059,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>475287</v>
+        <v>475077</v>
       </c>
       <c r="R52" t="n">
-        <v>6832747</v>
+        <v>6832687</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,7 +6094,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6165,7 +6104,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6192,14 +6131,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130041565</v>
+        <v>130041590</v>
       </c>
       <c r="B53" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -6227,10 +6166,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>475456</v>
+        <v>475119</v>
       </c>
       <c r="R53" t="n">
-        <v>6832651</v>
+        <v>6832699</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6262,7 +6201,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6272,7 +6211,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6299,14 +6238,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130041596</v>
+        <v>130041591</v>
       </c>
       <c r="B54" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -6334,10 +6273,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>475378</v>
+        <v>475155</v>
       </c>
       <c r="R54" t="n">
-        <v>6832576</v>
+        <v>6832695</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6369,7 +6308,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6379,7 +6318,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6406,14 +6345,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130041577</v>
+        <v>130041592</v>
       </c>
       <c r="B55" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -6441,10 +6380,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>475162</v>
+        <v>475196</v>
       </c>
       <c r="R55" t="n">
-        <v>6832756</v>
+        <v>6832709</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6476,7 +6415,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6486,7 +6425,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6513,32 +6452,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130041482</v>
+        <v>130041593</v>
       </c>
       <c r="B56" t="n">
-        <v>79204</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6548,10 +6487,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>475500</v>
+        <v>475269</v>
       </c>
       <c r="R56" t="n">
-        <v>6832632</v>
+        <v>6832659</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6583,7 +6522,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6593,7 +6532,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6620,32 +6559,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130041458</v>
+        <v>130041594</v>
       </c>
       <c r="B57" t="n">
-        <v>79770</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6655,10 +6594,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>475113</v>
+        <v>475287</v>
       </c>
       <c r="R57" t="n">
-        <v>6832543</v>
+        <v>6832631</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6690,7 +6629,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6700,7 +6639,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6727,32 +6666,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130041498</v>
+        <v>130041595</v>
       </c>
       <c r="B58" t="n">
-        <v>78938</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6762,10 +6701,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>475098</v>
+        <v>475334</v>
       </c>
       <c r="R58" t="n">
-        <v>6832700</v>
+        <v>6832589</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6797,7 +6736,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6807,7 +6746,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6834,14 +6773,14 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130041574</v>
+        <v>130041596</v>
       </c>
       <c r="B59" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -6869,10 +6808,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>475268</v>
+        <v>475378</v>
       </c>
       <c r="R59" t="n">
-        <v>6832805</v>
+        <v>6832576</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6904,7 +6843,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6914,7 +6853,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6941,32 +6880,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130041443</v>
+        <v>130041597</v>
       </c>
       <c r="B60" t="n">
-        <v>79212</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6976,10 +6915,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>475509</v>
+        <v>475391</v>
       </c>
       <c r="R60" t="n">
-        <v>6832511</v>
+        <v>6832581</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7011,7 +6950,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7021,7 +6960,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7048,50 +6987,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130041462</v>
+        <v>130041598</v>
       </c>
       <c r="B61" t="n">
-        <v>57016</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>475321</v>
+        <v>475394</v>
       </c>
       <c r="R61" t="n">
-        <v>6832648</v>
+        <v>6832587</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7123,7 +7057,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7133,12 +7067,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Under betad tall</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7165,32 +7094,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130041500</v>
+        <v>130041599</v>
       </c>
       <c r="B62" t="n">
-        <v>57930</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7200,10 +7129,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>475142</v>
+        <v>475445</v>
       </c>
       <c r="R62" t="n">
-        <v>6832509</v>
+        <v>6832596</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7235,7 +7164,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7245,7 +7174,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7272,32 +7201,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130041488</v>
+        <v>130041600</v>
       </c>
       <c r="B63" t="n">
-        <v>78938</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7307,10 +7236,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>475161</v>
+        <v>475471</v>
       </c>
       <c r="R63" t="n">
-        <v>6832601</v>
+        <v>6832571</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7342,7 +7271,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7352,7 +7281,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7379,14 +7308,14 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130041566</v>
+        <v>130044470</v>
       </c>
       <c r="B64" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -7408,16 +7337,19 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>475443</v>
+        <v>475494</v>
       </c>
       <c r="R64" t="n">
-        <v>6832633</v>
+        <v>6832601</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7447,53 +7379,44 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130041598</v>
+        <v>130044472</v>
       </c>
       <c r="B65" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -7515,16 +7438,19 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>475394</v>
+        <v>475467</v>
       </c>
       <c r="R65" t="n">
-        <v>6832587</v>
+        <v>6832594</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7554,53 +7480,44 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130041586</v>
+        <v>130044480</v>
       </c>
       <c r="B66" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -7622,16 +7539,19 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>475055</v>
+        <v>475417</v>
       </c>
       <c r="R66" t="n">
-        <v>6832711</v>
+        <v>6832617</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7661,53 +7581,44 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130041563</v>
+        <v>130044484</v>
       </c>
       <c r="B67" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -7729,16 +7640,19 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>475527</v>
+        <v>475322</v>
       </c>
       <c r="R67" t="n">
-        <v>6832623</v>
+        <v>6832694</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7768,53 +7682,44 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130041568</v>
+        <v>130044501</v>
       </c>
       <c r="B68" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -7836,16 +7741,19 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>475381</v>
+        <v>475263</v>
       </c>
       <c r="R68" t="n">
-        <v>6832661</v>
+        <v>6832664</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7875,53 +7783,44 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130041567</v>
+        <v>130044543</v>
       </c>
       <c r="B69" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -7943,16 +7842,19 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>475450</v>
+        <v>475221</v>
       </c>
       <c r="R69" t="n">
-        <v>6832632</v>
+        <v>6832703</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7982,53 +7884,44 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130041564</v>
+        <v>130044550</v>
       </c>
       <c r="B70" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -8050,16 +7943,19 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>475461</v>
+        <v>475214</v>
       </c>
       <c r="R70" t="n">
-        <v>6832659</v>
+        <v>6832713</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8089,89 +7985,78 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130041463</v>
+        <v>130044565</v>
       </c>
       <c r="B71" t="n">
-        <v>57016</v>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>475317</v>
+        <v>475192</v>
       </c>
       <c r="R71" t="n">
-        <v>6832770</v>
+        <v>6832673</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8201,94 +8086,78 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Under betad tall</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130041471</v>
+        <v>130044571</v>
       </c>
       <c r="B72" t="n">
-        <v>57823</v>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>475067</v>
+        <v>475209</v>
       </c>
       <c r="R72" t="n">
-        <v>6832760</v>
+        <v>6832640</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8318,49 +8187,40 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130041466</v>
+        <v>130041482</v>
       </c>
       <c r="B73" t="n">
-        <v>57016</v>
+        <v>79351</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8368,39 +8228,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>475445</v>
+        <v>475500</v>
       </c>
       <c r="R73" t="n">
-        <v>6832605</v>
+        <v>6832632</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8432,7 +8287,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8442,7 +8297,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8469,32 +8324,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130041528</v>
+        <v>130041483</v>
       </c>
       <c r="B74" t="n">
-        <v>79180</v>
+        <v>79351</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8504,10 +8359,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>475072</v>
+        <v>475269</v>
       </c>
       <c r="R74" t="n">
-        <v>6832555</v>
+        <v>6832659</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8539,7 +8394,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8549,7 +8404,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8576,10 +8431,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130041589</v>
+        <v>130041608</v>
       </c>
       <c r="B75" t="n">
-        <v>79180</v>
+        <v>78730</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8587,21 +8442,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8611,10 +8466,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>475077</v>
+        <v>475113</v>
       </c>
       <c r="R75" t="n">
-        <v>6832687</v>
+        <v>6832544</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8646,7 +8501,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8656,7 +8511,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8683,10 +8538,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130041542</v>
+        <v>130060248</v>
       </c>
       <c r="B76" t="n">
-        <v>79180</v>
+        <v>78730</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8694,34 +8549,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>475107</v>
+        <v>475301</v>
       </c>
       <c r="R76" t="n">
-        <v>6832635</v>
+        <v>6832730</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8751,49 +8609,40 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130041523</v>
+        <v>130041429</v>
       </c>
       <c r="B77" t="n">
-        <v>79180</v>
+        <v>79946</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8801,21 +8650,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8825,10 +8674,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>475171</v>
+        <v>475441</v>
       </c>
       <c r="R77" t="n">
-        <v>6832605</v>
+        <v>6832541</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8860,7 +8709,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8870,7 +8719,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8897,10 +8746,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130041580</v>
+        <v>130041430</v>
       </c>
       <c r="B78" t="n">
-        <v>79180</v>
+        <v>79946</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8908,21 +8757,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8932,10 +8781,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>475066</v>
+        <v>475161</v>
       </c>
       <c r="R78" t="n">
-        <v>6832769</v>
+        <v>6832599</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8967,7 +8816,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8977,7 +8826,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9004,10 +8853,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130044550</v>
+        <v>130041442</v>
       </c>
       <c r="B79" t="n">
-        <v>79180</v>
+        <v>79946</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9015,37 +8864,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>475214</v>
+        <v>475303</v>
       </c>
       <c r="R79" t="n">
-        <v>6832713</v>
+        <v>6832754</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9075,72 +8921,76 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130044477</v>
+        <v>130044552</v>
       </c>
       <c r="B80" t="n">
-        <v>57016</v>
+        <v>79946</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9148,10 +8998,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>475417</v>
+        <v>475214</v>
       </c>
       <c r="R80" t="n">
-        <v>6832617</v>
+        <v>6832713</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9192,6 +9042,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9210,48 +9061,50 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130044472</v>
+        <v>130041471</v>
       </c>
       <c r="B81" t="n">
-        <v>79180</v>
+        <v>57950</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>475467</v>
+        <v>475067</v>
       </c>
       <c r="R81" t="n">
-        <v>6832594</v>
+        <v>6832760</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9281,40 +9134,49 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130044543</v>
+        <v>130041461</v>
       </c>
       <c r="B82" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9322,37 +9184,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>475221</v>
+        <v>475283</v>
       </c>
       <c r="R82" t="n">
-        <v>6832703</v>
+        <v>6832744</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9382,40 +9246,49 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF82" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130044494</v>
+        <v>130041473</v>
       </c>
       <c r="B83" t="n">
-        <v>79770</v>
+        <v>57953</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9423,37 +9296,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>475301</v>
+        <v>475044</v>
       </c>
       <c r="R83" t="n">
-        <v>6832730</v>
+        <v>6832743</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9483,14 +9358,24 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>3 hål,2 och 8 meter upp, diameter 3 och 6 cm</t>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9499,29 +9384,28 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130044473</v>
+        <v>130041475</v>
       </c>
       <c r="B84" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9547,24 +9431,21 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>475417</v>
+        <v>475277</v>
       </c>
       <c r="R84" t="n">
-        <v>6832617</v>
+        <v>6832740</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9594,9 +9475,24 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran), högst 5 år gamla</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9611,22 +9507,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130044470</v>
+        <v>130041476</v>
       </c>
       <c r="B85" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9634,37 +9530,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>475494</v>
+        <v>475245</v>
       </c>
       <c r="R85" t="n">
-        <v>6832601</v>
+        <v>6832734</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9694,40 +9592,54 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130044482</v>
+        <v>130041478</v>
       </c>
       <c r="B86" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9753,24 +9665,21 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>475342</v>
+        <v>475186</v>
       </c>
       <c r="R86" t="n">
-        <v>6832644</v>
+        <v>6832701</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9800,9 +9709,24 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9817,22 +9741,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130044484</v>
+        <v>130044473</v>
       </c>
       <c r="B87" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9840,26 +9764,31 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9867,10 +9796,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>475322</v>
+        <v>475417</v>
       </c>
       <c r="R87" t="n">
-        <v>6832694</v>
+        <v>6832617</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9911,7 +9840,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9930,10 +9858,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130044486</v>
+        <v>130044481</v>
       </c>
       <c r="B88" t="n">
-        <v>91728</v>
+        <v>57953</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9941,26 +9869,31 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9968,10 +9901,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>475308</v>
+        <v>475386</v>
       </c>
       <c r="R88" t="n">
-        <v>6832714</v>
+        <v>6832591</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10012,7 +9945,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -10031,10 +9963,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130044552</v>
+        <v>130044482</v>
       </c>
       <c r="B89" t="n">
-        <v>79799</v>
+        <v>57953</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10042,26 +9974,31 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10069,10 +10006,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>475214</v>
+        <v>475342</v>
       </c>
       <c r="R89" t="n">
-        <v>6832713</v>
+        <v>6832644</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10113,7 +10050,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10132,48 +10068,50 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130044501</v>
+        <v>130041462</v>
       </c>
       <c r="B90" t="n">
-        <v>79180</v>
+        <v>57141</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>475263</v>
+        <v>475321</v>
       </c>
       <c r="R90" t="n">
-        <v>6832664</v>
+        <v>6832648</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10203,78 +10141,94 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Under betad tall</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130044571</v>
+        <v>130041463</v>
       </c>
       <c r="B91" t="n">
-        <v>79180</v>
+        <v>57141</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>475209</v>
+        <v>475317</v>
       </c>
       <c r="R91" t="n">
-        <v>6832640</v>
+        <v>6832770</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10304,83 +10258,94 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Under betad tall</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130044481</v>
+        <v>130041464</v>
       </c>
       <c r="B92" t="n">
-        <v>57826</v>
+        <v>57141</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>475386</v>
+        <v>475156</v>
       </c>
       <c r="R92" t="n">
-        <v>6832591</v>
+        <v>6832751</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10410,9 +10375,19 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10427,60 +10402,62 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130044565</v>
+        <v>130041465</v>
       </c>
       <c r="B93" t="n">
-        <v>79180</v>
+        <v>57141</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>475192</v>
+        <v>475430</v>
       </c>
       <c r="R93" t="n">
-        <v>6832673</v>
+        <v>6832587</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10510,78 +10487,89 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130044480</v>
+        <v>130041466</v>
       </c>
       <c r="B94" t="n">
-        <v>79180</v>
+        <v>57141</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>475417</v>
+        <v>475445</v>
       </c>
       <c r="R94" t="n">
-        <v>6832617</v>
+        <v>6832605</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10611,67 +10599,81 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130060248</v>
+        <v>130044477</v>
       </c>
       <c r="B95" t="n">
-        <v>78583</v>
+        <v>57141</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10679,10 +10681,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>475301</v>
+        <v>475417</v>
       </c>
       <c r="R95" t="n">
-        <v>6832730</v>
+        <v>6832617</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10723,7 +10725,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10739,6 +10740,540 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>130041500</v>
+      </c>
+      <c r="B96" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>475142</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6832509</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>130041488</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>475161</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6832601</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>130041498</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>475098</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6832700</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>130041458</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>475113</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6832543</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>130044494</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>475301</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6832730</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>3 hål,2 och 8 meter upp, diameter 3 och 6 cm</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54495-2025 artfynd.xlsx
+++ b/artfynd/A 54495-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY100"/>
+  <dimension ref="A1:AZ100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041443</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041447</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041448</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041449</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041450</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041602</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041603</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041502</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1629,6 +1674,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044486</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1741,6 +1791,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041518</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1848,6 +1903,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041522</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1955,6 +2015,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041523</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2062,6 +2127,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041524</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2169,6 +2239,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041525</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2276,6 +2351,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041526</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2383,6 +2463,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041527</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2490,6 +2575,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041528</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2597,6 +2687,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041529</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2704,6 +2799,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041530</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2811,6 +2911,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041531</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2918,6 +3023,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041532</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3025,6 +3135,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041540</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3132,6 +3247,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041542</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3239,6 +3359,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041543</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3346,6 +3471,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041544</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3453,6 +3583,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041562</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3560,6 +3695,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041563</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3667,6 +3807,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041564</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3774,6 +3919,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041565</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3881,6 +4031,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041566</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3988,6 +4143,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041567</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4095,6 +4255,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041568</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4202,6 +4367,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041569</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4309,6 +4479,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041570</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4416,6 +4591,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041571</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4523,6 +4703,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041572</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4630,6 +4815,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041573</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4737,6 +4927,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041574</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4844,6 +5039,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041575</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4951,6 +5151,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041576</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5058,6 +5263,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041577</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5165,6 +5375,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041578</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5272,6 +5487,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041579</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5379,6 +5599,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041580</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5486,6 +5711,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041582</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5593,6 +5823,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041583</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5700,6 +5935,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041584</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5807,6 +6047,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041585</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5914,6 +6159,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041586</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6021,6 +6271,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041588</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6128,6 +6383,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041589</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6235,6 +6495,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041590</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6342,6 +6607,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041591</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6449,6 +6719,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041592</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6556,6 +6831,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041593</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6663,6 +6943,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041594</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6770,6 +7055,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041595</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6877,6 +7167,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041596</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6984,6 +7279,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041597</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7091,6 +7391,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041598</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7198,6 +7503,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041599</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7305,6 +7615,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041600</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7406,6 +7721,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044470</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7507,6 +7827,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044472</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7608,6 +7933,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044480</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7709,6 +8039,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044484</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7810,6 +8145,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044501</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7911,6 +8251,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044543</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8012,6 +8357,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044550</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8113,6 +8463,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044565</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8214,6 +8569,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044571</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8321,6 +8681,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041482</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8428,6 +8793,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041483</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8535,6 +8905,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041608</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8636,6 +9011,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130060248</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8743,6 +9123,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041429</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8850,6 +9235,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041430</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8957,6 +9347,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041442</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9058,6 +9453,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044552</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9170,6 +9570,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041471</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9282,6 +9687,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041461</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9399,6 +9809,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041473</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9516,6 +9931,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041475</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9633,6 +10053,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041476</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9750,6 +10175,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041478</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9855,6 +10285,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044473</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9960,6 +10395,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044481</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10065,6 +10505,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044482</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10182,6 +10627,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041462</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10299,6 +10749,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041463</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10411,6 +10866,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041464</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10523,6 +10983,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041465</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10635,6 +11100,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041466</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10740,6 +11210,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044477</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10847,6 +11322,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041500</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10954,6 +11434,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041488</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11061,6 +11546,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041498</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11168,6 +11658,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041458</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11274,8 +11769,114 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044494</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>